--- a/ESIR_Master_Tracker.xlsx
+++ b/ESIR_Master_Tracker.xlsx
@@ -573,28 +573,26 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TBL_TestMaster" displayName="TBL_TestMaster" ref="A8:F30" headerRowCount="1">
-  <autoFilter ref="A8:F30"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TBL_TestCatalog" displayName="TBL_TestCatalog" ref="A8:D23" headerRowCount="1">
+  <autoFilter ref="A8:D23"/>
+  <tableColumns count="4">
     <tableColumn id="1" name="TestNameKR"/>
     <tableColumn id="2" name="TestType"/>
     <tableColumn id="3" name="Spec"/>
     <tableColumn id="4" name="DurationDays"/>
-    <tableColumn id="5" name="PartName"/>
-    <tableColumn id="6" name="PartCategory"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TBL_VehicleParts" displayName="TBL_VehicleParts" ref="A33:B51" headerRowCount="1">
-  <autoFilter ref="A33:B51"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TBL_PartMap" displayName="TBL_PartMap" ref="A26:B32" headerRowCount="1">
+  <autoFilter ref="A26:B32"/>
   <tableColumns count="2">
-    <tableColumn id="1" name="VPKey"/>
-    <tableColumn id="2" name="SupplierCode"/>
+    <tableColumn id="1" name="PartName"/>
+    <tableColumn id="2" name="PartCategory"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -924,15 +922,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
@@ -1112,7 +1110,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>TBL_TestMaster (시험 마스터)</t>
+          <t>TBL_TestCatalog (시험 카탈로그)</t>
         </is>
       </c>
     </row>
@@ -1137,16 +1135,6 @@
           <t>DurationDays</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>PartName</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>PartCategory</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -1167,21 +1155,11 @@
       <c r="D9" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Center Console Assy</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Console</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>내열 시험</t>
+          <t>내후성 시험</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -1191,27 +1169,17 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>MS-300-31</t>
+          <t>MS-300-34</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Center Console Assy</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>Console</t>
-        </is>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>마모 시험</t>
+          <t>내열 시험</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -1221,27 +1189,17 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>MS-300-35</t>
+          <t>MS-300-31</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Center Console Assy</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Console</t>
-        </is>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>치수 검사</t>
+          <t>마모 시험</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -1251,27 +1209,17 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>ES-90101</t>
+          <t>MS-300-35</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Center Console Assy</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Console</t>
-        </is>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>VOC 방출 시험</t>
+          <t>힌지 내구 시험</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1281,27 +1229,17 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>MS-300-57</t>
+          <t>ES-92030</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>Console Lid Assy</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Console</t>
-        </is>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>힌지 내구 시험</t>
+          <t>시트 내구 시험</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -1311,27 +1249,17 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>ES-92030</t>
+          <t>ES-93100</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>Console Lid Assy</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Console</t>
-        </is>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>외관 검사</t>
+          <t>연소성 시험</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1341,87 +1269,57 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>ES-90100</t>
+          <t>FMVSS 302</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>Console Lid Assy</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Console</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>VOC 방출 시험</t>
+          <t>안전벨트 앵커리지</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>단품 Component</t>
+          <t>차량장착 Vehicle</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>MS-300-57</t>
+          <t>FMVSS 210</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Door Trim LH</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>Trim</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>내후성 시험</t>
+          <t>ISOFIX 강도 시험</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>단품 Component</t>
+          <t>차량장착 Vehicle</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>MS-300-34</t>
+          <t>ECE R14</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>Door Trim LH</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Trim</t>
-        </is>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>연소성 시험</t>
+          <t>암레스트 하중</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -1431,27 +1329,17 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>FMVSS 302</t>
+          <t>ES-91200</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>Door Trim LH</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>Trim</t>
-        </is>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>외관 검사</t>
+          <t>치수 검사</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -1461,87 +1349,57 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>ES-90100</t>
+          <t>ES-90101</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>Door Trim LH</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>Trim</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>내후성 시험</t>
+          <t>H-Point 검증</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>단품 Component</t>
+          <t>차량장착 Vehicle</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>MS-300-34</t>
+          <t>ES-93000</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>Pillar Trim C</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>Trim</t>
-        </is>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>연소성 시험</t>
+          <t>BSR 시험</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>단품 Component</t>
+          <t>차량장착 Vehicle</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>FMVSS 302</t>
+          <t>ES-90500</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>Pillar Trim C</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Trim</t>
-        </is>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>치수 검사</t>
+          <t>외관 검사</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -1551,656 +1409,121 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>ES-90101</t>
+          <t>ES-90100</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>Pillar Trim C</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>Trim</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>시트 내구 시험</t>
+          <t>수하물 충격 시험</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>단품 Component</t>
+          <t>차량장착 Vehicle</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>ES-93100</t>
+          <t>ECE R17</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>Front Seat Assy LH</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Seat</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>안전벨트 앵커리지</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>차량장착 Vehicle</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>FMVSS 210</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>Front Seat Assy LH</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>Seat</t>
-        </is>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>H-Point 검증</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>차량장착 Vehicle</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>ES-93000</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>Front Seat Assy LH</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Seat</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>TBL_PartMap (부품→구분)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>BSR 시험</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>차량장착 Vehicle</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>ES-90500</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>Front Seat Assy LH</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>Seat</t>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>PartName</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>PartCategory</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>시트 내구 시험</t>
+          <t>Center Console Assy</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>단품 Component</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>ES-93100</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>Rear Seat Assy</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Seat</t>
+          <t>Console</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>ISOFIX 강도 시험</t>
+          <t>Console Lid Assy</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>차량장착 Vehicle</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>ECE R14</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>Rear Seat Assy</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>Seat</t>
+          <t>Console</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>수하물 충격 시험</t>
+          <t>Door Trim LH</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>차량장착 Vehicle</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>ECE R17</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>Rear Seat Assy</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Seat</t>
+          <t>Trim</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>외관 검사</t>
+          <t>Pillar Trim C</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>단품 Component</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>ES-90100</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
+          <t>Trim</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Front Seat Assy LH</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Seat</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>Rear Seat Assy</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Seat</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>TBL_VehicleParts (차종×부품→협력사)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>VPKey</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>SupplierCode</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>AE_PE_Center Console Assy</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>SUP_A</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>AE_PE_Console Lid Assy</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>SUP_A</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>AE_PE_Door Trim LH</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>SUP_B</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>AE_PE_Pillar Trim C</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>SUP_C</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>AE_PE_Front Seat Assy LH</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>SUP_D</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>AE_PE_Rear Seat Assy</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>SUP_D</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>SU2i_Center Console Assy</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>SUP_B</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>SU2i_Console Lid Assy</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>SUP_B</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>SU2i_Door Trim LH</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>SUP_C</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>SU2i_Pillar Trim C</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>SUP_A</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>SU2i_Front Seat Assy LH</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>SUP_D</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>SU2i_Rear Seat Assy</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>SUP_D</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>EN_SUV_Center Console Assy</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>SUP_C</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>EN_SUV_Console Lid Assy</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>SUP_A</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>EN_SUV_Door Trim LH</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>SUP_B</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>EN_SUV_Pillar Trim C</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>SUP_B</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>EN_SUV_Front Seat Assy LH</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>SUP_D</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>EN_SUV_Rear Seat Assy</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>SUP_D</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Dropdown: PartNames</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>Center Console Assy</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>Console Lid Assy</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>Door Trim LH</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>Pillar Trim C</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>Front Seat Assy LH</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>Rear Seat Assy</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>Dropdown: TestNames</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>VOC 방출 시험</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t>내후성 시험</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>내열 시험</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>마모 시험</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>힌지 내구 시험</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="7" t="inlineStr">
-        <is>
-          <t>시트 내구 시험</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t>연소성 시험</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="7" t="inlineStr">
-        <is>
-          <t>안전벨트 앵커리지</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="7" t="inlineStr">
-        <is>
-          <t>ISOFIX 강도 시험</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="7" t="inlineStr">
-        <is>
-          <t>암레스트 하중</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="7" t="inlineStr">
-        <is>
-          <t>치수 검사</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="7" t="inlineStr">
-        <is>
-          <t>H-Point 검증</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="7" t="inlineStr">
-        <is>
-          <t>BSR 시험</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="7" t="inlineStr">
-        <is>
-          <t>외관 검사</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="7" t="inlineStr">
-        <is>
-          <t>수하물 충격 시험</t>
         </is>
       </c>
     </row>
@@ -2340,7 +1663,7 @@
           <t>Test Type</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
@@ -2482,7 +1805,7 @@
           <t>시험유형</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>협력사</t>
         </is>
@@ -2593,7 +1916,7 @@
         </is>
       </c>
       <c r="D5" s="15">
-        <f>IFERROR(VLOOKUP(C5,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C5,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -2602,13 +1925,10 @@
         </is>
       </c>
       <c r="F5" s="15">
-        <f>IFERROR(VLOOKUP(E5,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G5" s="15">
-        <f>IFERROR(VLOOKUP(B5&amp;"_"&amp;C5,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E5,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="13" t="n"/>
       <c r="H5" s="16">
         <f>IFERROR(VLOOKUP(B5,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -2630,7 +1950,7 @@
       </c>
       <c r="O5" s="13" t="n"/>
       <c r="P5" s="16">
-        <f>IFERROR(N5+VLOOKUP(E5,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N5+VLOOKUP(E5,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q5" s="13" t="n"/>
@@ -2676,7 +1996,7 @@
         </is>
       </c>
       <c r="D6" s="15">
-        <f>IFERROR(VLOOKUP(C6,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C6,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -2685,13 +2005,10 @@
         </is>
       </c>
       <c r="F6" s="15">
-        <f>IFERROR(VLOOKUP(E6,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G6" s="15">
-        <f>IFERROR(VLOOKUP(B6&amp;"_"&amp;C6,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E6,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="13" t="n"/>
       <c r="H6" s="16">
         <f>IFERROR(VLOOKUP(B6,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -2719,7 +2036,7 @@
       </c>
       <c r="O6" s="13" t="n"/>
       <c r="P6" s="16">
-        <f>IFERROR(N6+VLOOKUP(E6,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N6+VLOOKUP(E6,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q6" s="13" t="n"/>
@@ -2765,7 +2082,7 @@
         </is>
       </c>
       <c r="D7" s="15">
-        <f>IFERROR(VLOOKUP(C7,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C7,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -2774,13 +2091,10 @@
         </is>
       </c>
       <c r="F7" s="15">
-        <f>IFERROR(VLOOKUP(E7,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G7" s="15">
-        <f>IFERROR(VLOOKUP(B7&amp;"_"&amp;C7,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E7,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="13" t="n"/>
       <c r="H7" s="16">
         <f>IFERROR(VLOOKUP(B7,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -2812,7 +2126,7 @@
         <v>46102</v>
       </c>
       <c r="P7" s="16">
-        <f>IFERROR(N7+VLOOKUP(E7,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N7+VLOOKUP(E7,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q7" s="13" t="n"/>
@@ -2858,7 +2172,7 @@
         </is>
       </c>
       <c r="D8" s="15">
-        <f>IFERROR(VLOOKUP(C8,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C8,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -2867,13 +2181,10 @@
         </is>
       </c>
       <c r="F8" s="15">
-        <f>IFERROR(VLOOKUP(E8,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G8" s="15">
-        <f>IFERROR(VLOOKUP(B8&amp;"_"&amp;C8,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E8,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="13" t="n"/>
       <c r="H8" s="16">
         <f>IFERROR(VLOOKUP(B8,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -2905,7 +2216,7 @@
         <v>46103</v>
       </c>
       <c r="P8" s="16">
-        <f>IFERROR(N8+VLOOKUP(E8,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N8+VLOOKUP(E8,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q8" s="20" t="n">
@@ -2955,7 +2266,7 @@
         </is>
       </c>
       <c r="D9" s="15">
-        <f>IFERROR(VLOOKUP(C9,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C9,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -2964,13 +2275,10 @@
         </is>
       </c>
       <c r="F9" s="15">
-        <f>IFERROR(VLOOKUP(E9,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G9" s="15">
-        <f>IFERROR(VLOOKUP(B9&amp;"_"&amp;C9,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E9,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="13" t="n"/>
       <c r="H9" s="16">
         <f>IFERROR(VLOOKUP(B9,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -2994,7 +2302,7 @@
       </c>
       <c r="O9" s="13" t="n"/>
       <c r="P9" s="16">
-        <f>IFERROR(N9+VLOOKUP(E9,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N9+VLOOKUP(E9,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q9" s="13" t="n"/>
@@ -3040,7 +2348,7 @@
         </is>
       </c>
       <c r="D10" s="15">
-        <f>IFERROR(VLOOKUP(C10,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C10,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E10" s="14" t="inlineStr">
@@ -3049,13 +2357,10 @@
         </is>
       </c>
       <c r="F10" s="15">
-        <f>IFERROR(VLOOKUP(E10,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G10" s="15">
-        <f>IFERROR(VLOOKUP(B10&amp;"_"&amp;C10,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E10,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="13" t="n"/>
       <c r="H10" s="16">
         <f>IFERROR(VLOOKUP(B10,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -3085,7 +2390,7 @@
       </c>
       <c r="O10" s="13" t="n"/>
       <c r="P10" s="16">
-        <f>IFERROR(N10+VLOOKUP(E10,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N10+VLOOKUP(E10,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q10" s="13" t="n"/>
@@ -3131,7 +2436,7 @@
         </is>
       </c>
       <c r="D11" s="15">
-        <f>IFERROR(VLOOKUP(C11,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C11,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -3140,13 +2445,10 @@
         </is>
       </c>
       <c r="F11" s="15">
-        <f>IFERROR(VLOOKUP(E11,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G11" s="15">
-        <f>IFERROR(VLOOKUP(B11&amp;"_"&amp;C11,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E11,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="13" t="n"/>
       <c r="H11" s="16">
         <f>IFERROR(VLOOKUP(B11,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -3178,7 +2480,7 @@
         <v>46100</v>
       </c>
       <c r="P11" s="16">
-        <f>IFERROR(N11+VLOOKUP(E11,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N11+VLOOKUP(E11,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q11" s="20" t="n">
@@ -3228,7 +2530,7 @@
         </is>
       </c>
       <c r="D12" s="15">
-        <f>IFERROR(VLOOKUP(C12,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C12,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E12" s="14" t="inlineStr">
@@ -3237,13 +2539,10 @@
         </is>
       </c>
       <c r="F12" s="15">
-        <f>IFERROR(VLOOKUP(E12,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G12" s="15">
-        <f>IFERROR(VLOOKUP(B12&amp;"_"&amp;C12,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E12,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="13" t="n"/>
       <c r="H12" s="16">
         <f>IFERROR(VLOOKUP(B12,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -3271,7 +2570,7 @@
       </c>
       <c r="O12" s="13" t="n"/>
       <c r="P12" s="16">
-        <f>IFERROR(N12+VLOOKUP(E12,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N12+VLOOKUP(E12,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q12" s="13" t="n"/>
@@ -3317,7 +2616,7 @@
         </is>
       </c>
       <c r="D13" s="15">
-        <f>IFERROR(VLOOKUP(C13,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C13,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -3326,13 +2625,10 @@
         </is>
       </c>
       <c r="F13" s="15">
-        <f>IFERROR(VLOOKUP(E13,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G13" s="15">
-        <f>IFERROR(VLOOKUP(B13&amp;"_"&amp;C13,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E13,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="13" t="n"/>
       <c r="H13" s="16">
         <f>IFERROR(VLOOKUP(B13,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -3364,7 +2660,7 @@
         <v>46102</v>
       </c>
       <c r="P13" s="16">
-        <f>IFERROR(N13+VLOOKUP(E13,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N13+VLOOKUP(E13,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q13" s="20" t="n">
@@ -3412,7 +2708,7 @@
         </is>
       </c>
       <c r="D14" s="15">
-        <f>IFERROR(VLOOKUP(C14,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C14,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -3421,13 +2717,10 @@
         </is>
       </c>
       <c r="F14" s="15">
-        <f>IFERROR(VLOOKUP(E14,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G14" s="15">
-        <f>IFERROR(VLOOKUP(B14&amp;"_"&amp;C14,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E14,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="13" t="n"/>
       <c r="H14" s="16">
         <f>IFERROR(VLOOKUP(B14,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -3455,7 +2748,7 @@
       </c>
       <c r="O14" s="13" t="n"/>
       <c r="P14" s="16">
-        <f>IFERROR(N14+VLOOKUP(E14,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N14+VLOOKUP(E14,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q14" s="13" t="n"/>
@@ -3505,7 +2798,7 @@
         </is>
       </c>
       <c r="D15" s="15">
-        <f>IFERROR(VLOOKUP(C15,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C15,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -3514,13 +2807,10 @@
         </is>
       </c>
       <c r="F15" s="15">
-        <f>IFERROR(VLOOKUP(E15,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G15" s="15">
-        <f>IFERROR(VLOOKUP(B15&amp;"_"&amp;C15,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E15,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="13" t="n"/>
       <c r="H15" s="16">
         <f>IFERROR(VLOOKUP(B15,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -3552,7 +2842,7 @@
         <v>46104</v>
       </c>
       <c r="P15" s="16">
-        <f>IFERROR(N15+VLOOKUP(E15,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N15+VLOOKUP(E15,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q15" s="20" t="n">
@@ -3602,7 +2892,7 @@
         </is>
       </c>
       <c r="D16" s="15">
-        <f>IFERROR(VLOOKUP(C16,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C16,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E16" s="14" t="inlineStr">
@@ -3611,13 +2901,10 @@
         </is>
       </c>
       <c r="F16" s="15">
-        <f>IFERROR(VLOOKUP(E16,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G16" s="15">
-        <f>IFERROR(VLOOKUP(B16&amp;"_"&amp;C16,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E16,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="13" t="n"/>
       <c r="H16" s="16">
         <f>IFERROR(VLOOKUP(B16,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -3645,7 +2932,7 @@
       </c>
       <c r="O16" s="13" t="n"/>
       <c r="P16" s="16">
-        <f>IFERROR(N16+VLOOKUP(E16,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N16+VLOOKUP(E16,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q16" s="13" t="n"/>
@@ -3691,7 +2978,7 @@
         </is>
       </c>
       <c r="D17" s="15">
-        <f>IFERROR(VLOOKUP(C17,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C17,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E17" s="14" t="inlineStr">
@@ -3700,13 +2987,10 @@
         </is>
       </c>
       <c r="F17" s="15">
-        <f>IFERROR(VLOOKUP(E17,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G17" s="15">
-        <f>IFERROR(VLOOKUP(B17&amp;"_"&amp;C17,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E17,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="13" t="n"/>
       <c r="H17" s="16">
         <f>IFERROR(VLOOKUP(B17,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -3738,7 +3022,7 @@
         <v>46100</v>
       </c>
       <c r="P17" s="16">
-        <f>IFERROR(N17+VLOOKUP(E17,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N17+VLOOKUP(E17,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q17" s="13" t="n"/>
@@ -3784,7 +3068,7 @@
         </is>
       </c>
       <c r="D18" s="15">
-        <f>IFERROR(VLOOKUP(C18,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C18,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E18" s="14" t="inlineStr">
@@ -3793,13 +3077,10 @@
         </is>
       </c>
       <c r="F18" s="15">
-        <f>IFERROR(VLOOKUP(E18,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G18" s="15">
-        <f>IFERROR(VLOOKUP(B18&amp;"_"&amp;C18,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E18,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="13" t="n"/>
       <c r="H18" s="16">
         <f>IFERROR(VLOOKUP(B18,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -3831,7 +3112,7 @@
         <v>46101</v>
       </c>
       <c r="P18" s="16">
-        <f>IFERROR(N18+VLOOKUP(E18,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N18+VLOOKUP(E18,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q18" s="20" t="n">
@@ -3881,7 +3162,7 @@
         </is>
       </c>
       <c r="D19" s="15">
-        <f>IFERROR(VLOOKUP(C19,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C19,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E19" s="14" t="inlineStr">
@@ -3890,13 +3171,10 @@
         </is>
       </c>
       <c r="F19" s="15">
-        <f>IFERROR(VLOOKUP(E19,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G19" s="15">
-        <f>IFERROR(VLOOKUP(B19&amp;"_"&amp;C19,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E19,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="13" t="n"/>
       <c r="H19" s="16">
         <f>IFERROR(VLOOKUP(B19,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -3926,7 +3204,7 @@
       </c>
       <c r="O19" s="13" t="n"/>
       <c r="P19" s="16">
-        <f>IFERROR(N19+VLOOKUP(E19,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N19+VLOOKUP(E19,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q19" s="13" t="n"/>
@@ -3976,7 +3254,7 @@
         </is>
       </c>
       <c r="D20" s="15">
-        <f>IFERROR(VLOOKUP(C20,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C20,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E20" s="14" t="inlineStr">
@@ -3985,13 +3263,10 @@
         </is>
       </c>
       <c r="F20" s="15">
-        <f>IFERROR(VLOOKUP(E20,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G20" s="15">
-        <f>IFERROR(VLOOKUP(B20&amp;"_"&amp;C20,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E20,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="13" t="n"/>
       <c r="H20" s="16">
         <f>IFERROR(VLOOKUP(B20,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -4019,7 +3294,7 @@
       </c>
       <c r="O20" s="13" t="n"/>
       <c r="P20" s="16">
-        <f>IFERROR(N20+VLOOKUP(E20,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N20+VLOOKUP(E20,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q20" s="13" t="n"/>
@@ -4065,7 +3340,7 @@
         </is>
       </c>
       <c r="D21" s="15">
-        <f>IFERROR(VLOOKUP(C21,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C21,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E21" s="14" t="inlineStr">
@@ -4074,13 +3349,10 @@
         </is>
       </c>
       <c r="F21" s="15">
-        <f>IFERROR(VLOOKUP(E21,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G21" s="15">
-        <f>IFERROR(VLOOKUP(B21&amp;"_"&amp;C21,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E21,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="13" t="n"/>
       <c r="H21" s="16">
         <f>IFERROR(VLOOKUP(B21,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -4112,7 +3384,7 @@
         <v>46104</v>
       </c>
       <c r="P21" s="16">
-        <f>IFERROR(N21+VLOOKUP(E21,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N21+VLOOKUP(E21,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q21" s="13" t="n"/>
@@ -4158,7 +3430,7 @@
         </is>
       </c>
       <c r="D22" s="15">
-        <f>IFERROR(VLOOKUP(C22,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C22,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E22" s="14" t="inlineStr">
@@ -4167,13 +3439,10 @@
         </is>
       </c>
       <c r="F22" s="15">
-        <f>IFERROR(VLOOKUP(E22,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G22" s="15">
-        <f>IFERROR(VLOOKUP(B22&amp;"_"&amp;C22,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E22,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="13" t="n"/>
       <c r="H22" s="16">
         <f>IFERROR(VLOOKUP(B22,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -4205,7 +3474,7 @@
         <v>46099</v>
       </c>
       <c r="P22" s="16">
-        <f>IFERROR(N22+VLOOKUP(E22,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N22+VLOOKUP(E22,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q22" s="20" t="n">
@@ -4253,7 +3522,7 @@
         </is>
       </c>
       <c r="D23" s="15">
-        <f>IFERROR(VLOOKUP(C23,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C23,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E23" s="14" t="inlineStr">
@@ -4262,13 +3531,10 @@
         </is>
       </c>
       <c r="F23" s="15">
-        <f>IFERROR(VLOOKUP(E23,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G23" s="15">
-        <f>IFERROR(VLOOKUP(B23&amp;"_"&amp;C23,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E23,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="13" t="n"/>
       <c r="H23" s="16">
         <f>IFERROR(VLOOKUP(B23,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -4298,7 +3564,7 @@
       </c>
       <c r="O23" s="13" t="n"/>
       <c r="P23" s="16">
-        <f>IFERROR(N23+VLOOKUP(E23,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N23+VLOOKUP(E23,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q23" s="13" t="n"/>
@@ -4344,7 +3610,7 @@
         </is>
       </c>
       <c r="D24" s="15">
-        <f>IFERROR(VLOOKUP(C24,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C24,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E24" s="14" t="inlineStr">
@@ -4353,13 +3619,10 @@
         </is>
       </c>
       <c r="F24" s="15">
-        <f>IFERROR(VLOOKUP(E24,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G24" s="15">
-        <f>IFERROR(VLOOKUP(B24&amp;"_"&amp;C24,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E24,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="13" t="n"/>
       <c r="H24" s="16">
         <f>IFERROR(VLOOKUP(B24,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -4391,7 +3654,7 @@
         <v>46101</v>
       </c>
       <c r="P24" s="16">
-        <f>IFERROR(N24+VLOOKUP(E24,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N24+VLOOKUP(E24,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q24" s="20" t="n">
@@ -4445,7 +3708,7 @@
         </is>
       </c>
       <c r="D25" s="15">
-        <f>IFERROR(VLOOKUP(C25,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C25,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E25" s="14" t="inlineStr">
@@ -4454,13 +3717,10 @@
         </is>
       </c>
       <c r="F25" s="15">
-        <f>IFERROR(VLOOKUP(E25,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G25" s="15">
-        <f>IFERROR(VLOOKUP(B25&amp;"_"&amp;C25,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E25,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="13" t="n"/>
       <c r="H25" s="16">
         <f>IFERROR(VLOOKUP(B25,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -4492,7 +3752,7 @@
         <v>46102</v>
       </c>
       <c r="P25" s="16">
-        <f>IFERROR(N25+VLOOKUP(E25,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N25+VLOOKUP(E25,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q25" s="20" t="n">
@@ -4542,7 +3802,7 @@
         </is>
       </c>
       <c r="D26" s="15">
-        <f>IFERROR(VLOOKUP(C26,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C26,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E26" s="14" t="inlineStr">
@@ -4551,13 +3811,10 @@
         </is>
       </c>
       <c r="F26" s="15">
-        <f>IFERROR(VLOOKUP(E26,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G26" s="15">
-        <f>IFERROR(VLOOKUP(B26&amp;"_"&amp;C26,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E26,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="13" t="n"/>
       <c r="H26" s="16">
         <f>IFERROR(VLOOKUP(B26,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -4589,7 +3846,7 @@
         <v>46103</v>
       </c>
       <c r="P26" s="16">
-        <f>IFERROR(N26+VLOOKUP(E26,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N26+VLOOKUP(E26,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q26" s="20" t="n">
@@ -4639,7 +3896,7 @@
         </is>
       </c>
       <c r="D27" s="15">
-        <f>IFERROR(VLOOKUP(C27,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C27,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E27" s="14" t="inlineStr">
@@ -4648,13 +3905,10 @@
         </is>
       </c>
       <c r="F27" s="15">
-        <f>IFERROR(VLOOKUP(E27,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G27" s="15">
-        <f>IFERROR(VLOOKUP(B27&amp;"_"&amp;C27,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E27,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="13" t="n"/>
       <c r="H27" s="16">
         <f>IFERROR(VLOOKUP(B27,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -4676,7 +3930,7 @@
       </c>
       <c r="O27" s="13" t="n"/>
       <c r="P27" s="16">
-        <f>IFERROR(N27+VLOOKUP(E27,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N27+VLOOKUP(E27,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q27" s="13" t="n"/>
@@ -4722,7 +3976,7 @@
         </is>
       </c>
       <c r="D28" s="15">
-        <f>IFERROR(VLOOKUP(C28,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C28,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E28" s="14" t="inlineStr">
@@ -4731,13 +3985,10 @@
         </is>
       </c>
       <c r="F28" s="15">
-        <f>IFERROR(VLOOKUP(E28,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G28" s="15">
-        <f>IFERROR(VLOOKUP(B28&amp;"_"&amp;C28,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E28,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="13" t="n"/>
       <c r="H28" s="16">
         <f>IFERROR(VLOOKUP(B28,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -4765,7 +4016,7 @@
       </c>
       <c r="O28" s="13" t="n"/>
       <c r="P28" s="16">
-        <f>IFERROR(N28+VLOOKUP(E28,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N28+VLOOKUP(E28,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q28" s="13" t="n"/>
@@ -4811,7 +4062,7 @@
         </is>
       </c>
       <c r="D29" s="15">
-        <f>IFERROR(VLOOKUP(C29,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C29,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E29" s="14" t="inlineStr">
@@ -4820,13 +4071,10 @@
         </is>
       </c>
       <c r="F29" s="15">
-        <f>IFERROR(VLOOKUP(E29,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G29" s="15">
-        <f>IFERROR(VLOOKUP(B29&amp;"_"&amp;C29,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E29,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="13" t="n"/>
       <c r="H29" s="16">
         <f>IFERROR(VLOOKUP(B29,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -4858,7 +4106,7 @@
         <v>46145</v>
       </c>
       <c r="P29" s="16">
-        <f>IFERROR(N29+VLOOKUP(E29,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N29+VLOOKUP(E29,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q29" s="13" t="n"/>
@@ -4904,7 +4152,7 @@
         </is>
       </c>
       <c r="D30" s="15">
-        <f>IFERROR(VLOOKUP(C30,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C30,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E30" s="14" t="inlineStr">
@@ -4913,13 +4161,10 @@
         </is>
       </c>
       <c r="F30" s="15">
-        <f>IFERROR(VLOOKUP(E30,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G30" s="15">
-        <f>IFERROR(VLOOKUP(B30&amp;"_"&amp;C30,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E30,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="13" t="n"/>
       <c r="H30" s="16">
         <f>IFERROR(VLOOKUP(B30,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -4951,7 +4196,7 @@
         <v>46146</v>
       </c>
       <c r="P30" s="16">
-        <f>IFERROR(N30+VLOOKUP(E30,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N30+VLOOKUP(E30,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q30" s="20" t="n">
@@ -5001,7 +4246,7 @@
         </is>
       </c>
       <c r="D31" s="15">
-        <f>IFERROR(VLOOKUP(C31,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C31,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E31" s="14" t="inlineStr">
@@ -5010,13 +4255,10 @@
         </is>
       </c>
       <c r="F31" s="15">
-        <f>IFERROR(VLOOKUP(E31,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G31" s="15">
-        <f>IFERROR(VLOOKUP(B31&amp;"_"&amp;C31,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E31,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="13" t="n"/>
       <c r="H31" s="16">
         <f>IFERROR(VLOOKUP(B31,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -5040,7 +4282,7 @@
       </c>
       <c r="O31" s="13" t="n"/>
       <c r="P31" s="16">
-        <f>IFERROR(N31+VLOOKUP(E31,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N31+VLOOKUP(E31,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q31" s="13" t="n"/>
@@ -5086,7 +4328,7 @@
         </is>
       </c>
       <c r="D32" s="15">
-        <f>IFERROR(VLOOKUP(C32,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C32,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E32" s="14" t="inlineStr">
@@ -5095,13 +4337,10 @@
         </is>
       </c>
       <c r="F32" s="15">
-        <f>IFERROR(VLOOKUP(E32,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="15">
-        <f>IFERROR(VLOOKUP(B32&amp;"_"&amp;C32,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E32,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="13" t="n"/>
       <c r="H32" s="16">
         <f>IFERROR(VLOOKUP(B32,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -5131,7 +4370,7 @@
       </c>
       <c r="O32" s="13" t="n"/>
       <c r="P32" s="16">
-        <f>IFERROR(N32+VLOOKUP(E32,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N32+VLOOKUP(E32,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q32" s="13" t="n"/>
@@ -5177,7 +4416,7 @@
         </is>
       </c>
       <c r="D33" s="15">
-        <f>IFERROR(VLOOKUP(C33,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C33,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E33" s="14" t="inlineStr">
@@ -5186,13 +4425,10 @@
         </is>
       </c>
       <c r="F33" s="15">
-        <f>IFERROR(VLOOKUP(E33,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G33" s="15">
-        <f>IFERROR(VLOOKUP(B33&amp;"_"&amp;C33,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E33,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="13" t="n"/>
       <c r="H33" s="16">
         <f>IFERROR(VLOOKUP(B33,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -5224,7 +4460,7 @@
         <v>46149</v>
       </c>
       <c r="P33" s="16">
-        <f>IFERROR(N33+VLOOKUP(E33,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N33+VLOOKUP(E33,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q33" s="20" t="n">
@@ -5274,7 +4510,7 @@
         </is>
       </c>
       <c r="D34" s="15">
-        <f>IFERROR(VLOOKUP(C34,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C34,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E34" s="14" t="inlineStr">
@@ -5283,13 +4519,10 @@
         </is>
       </c>
       <c r="F34" s="15">
-        <f>IFERROR(VLOOKUP(E34,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G34" s="15">
-        <f>IFERROR(VLOOKUP(B34&amp;"_"&amp;C34,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E34,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="13" t="n"/>
       <c r="H34" s="16">
         <f>IFERROR(VLOOKUP(B34,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -5317,7 +4550,7 @@
       </c>
       <c r="O34" s="13" t="n"/>
       <c r="P34" s="16">
-        <f>IFERROR(N34+VLOOKUP(E34,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N34+VLOOKUP(E34,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q34" s="13" t="n"/>
@@ -5363,7 +4596,7 @@
         </is>
       </c>
       <c r="D35" s="15">
-        <f>IFERROR(VLOOKUP(C35,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C35,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E35" s="14" t="inlineStr">
@@ -5372,13 +4605,10 @@
         </is>
       </c>
       <c r="F35" s="15">
-        <f>IFERROR(VLOOKUP(E35,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G35" s="15">
-        <f>IFERROR(VLOOKUP(B35&amp;"_"&amp;C35,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E35,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="13" t="n"/>
       <c r="H35" s="16">
         <f>IFERROR(VLOOKUP(B35,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -5410,7 +4640,7 @@
         <v>46145</v>
       </c>
       <c r="P35" s="16">
-        <f>IFERROR(N35+VLOOKUP(E35,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N35+VLOOKUP(E35,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q35" s="20" t="n">
@@ -5458,7 +4688,7 @@
         </is>
       </c>
       <c r="D36" s="15">
-        <f>IFERROR(VLOOKUP(C36,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C36,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E36" s="14" t="inlineStr">
@@ -5467,13 +4697,10 @@
         </is>
       </c>
       <c r="F36" s="15">
-        <f>IFERROR(VLOOKUP(E36,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G36" s="15">
-        <f>IFERROR(VLOOKUP(B36&amp;"_"&amp;C36,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E36,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="13" t="n"/>
       <c r="H36" s="16">
         <f>IFERROR(VLOOKUP(B36,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -5501,7 +4728,7 @@
       </c>
       <c r="O36" s="13" t="n"/>
       <c r="P36" s="16">
-        <f>IFERROR(N36+VLOOKUP(E36,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N36+VLOOKUP(E36,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q36" s="13" t="n"/>
@@ -5551,7 +4778,7 @@
         </is>
       </c>
       <c r="D37" s="15">
-        <f>IFERROR(VLOOKUP(C37,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C37,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E37" s="14" t="inlineStr">
@@ -5560,13 +4787,10 @@
         </is>
       </c>
       <c r="F37" s="15">
-        <f>IFERROR(VLOOKUP(E37,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G37" s="15">
-        <f>IFERROR(VLOOKUP(B37&amp;"_"&amp;C37,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E37,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="13" t="n"/>
       <c r="H37" s="16">
         <f>IFERROR(VLOOKUP(B37,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -5598,7 +4822,7 @@
         <v>46147</v>
       </c>
       <c r="P37" s="16">
-        <f>IFERROR(N37+VLOOKUP(E37,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N37+VLOOKUP(E37,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q37" s="20" t="n">
@@ -5648,7 +4872,7 @@
         </is>
       </c>
       <c r="D38" s="15">
-        <f>IFERROR(VLOOKUP(C38,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C38,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E38" s="14" t="inlineStr">
@@ -5657,13 +4881,10 @@
         </is>
       </c>
       <c r="F38" s="15">
-        <f>IFERROR(VLOOKUP(E38,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G38" s="15">
-        <f>IFERROR(VLOOKUP(B38&amp;"_"&amp;C38,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E38,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="13" t="n"/>
       <c r="H38" s="16">
         <f>IFERROR(VLOOKUP(B38,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -5691,7 +4912,7 @@
       </c>
       <c r="O38" s="13" t="n"/>
       <c r="P38" s="16">
-        <f>IFERROR(N38+VLOOKUP(E38,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N38+VLOOKUP(E38,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q38" s="13" t="n"/>
@@ -5737,7 +4958,7 @@
         </is>
       </c>
       <c r="D39" s="15">
-        <f>IFERROR(VLOOKUP(C39,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C39,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E39" s="14" t="inlineStr">
@@ -5746,13 +4967,10 @@
         </is>
       </c>
       <c r="F39" s="15">
-        <f>IFERROR(VLOOKUP(E39,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G39" s="15">
-        <f>IFERROR(VLOOKUP(B39&amp;"_"&amp;C39,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E39,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="13" t="n"/>
       <c r="H39" s="16">
         <f>IFERROR(VLOOKUP(B39,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -5784,7 +5002,7 @@
         <v>46149</v>
       </c>
       <c r="P39" s="16">
-        <f>IFERROR(N39+VLOOKUP(E39,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N39+VLOOKUP(E39,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q39" s="13" t="n"/>
@@ -5830,7 +5048,7 @@
         </is>
       </c>
       <c r="D40" s="15">
-        <f>IFERROR(VLOOKUP(C40,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C40,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E40" s="14" t="inlineStr">
@@ -5839,13 +5057,10 @@
         </is>
       </c>
       <c r="F40" s="15">
-        <f>IFERROR(VLOOKUP(E40,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G40" s="15">
-        <f>IFERROR(VLOOKUP(B40&amp;"_"&amp;C40,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E40,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="13" t="n"/>
       <c r="H40" s="16">
         <f>IFERROR(VLOOKUP(B40,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -5877,7 +5092,7 @@
         <v>46144</v>
       </c>
       <c r="P40" s="16">
-        <f>IFERROR(N40+VLOOKUP(E40,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N40+VLOOKUP(E40,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q40" s="20" t="n">
@@ -5927,7 +5142,7 @@
         </is>
       </c>
       <c r="D41" s="15">
-        <f>IFERROR(VLOOKUP(C41,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C41,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E41" s="14" t="inlineStr">
@@ -5936,13 +5151,10 @@
         </is>
       </c>
       <c r="F41" s="15">
-        <f>IFERROR(VLOOKUP(E41,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G41" s="15">
-        <f>IFERROR(VLOOKUP(B41&amp;"_"&amp;C41,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E41,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="13" t="n"/>
       <c r="H41" s="16">
         <f>IFERROR(VLOOKUP(B41,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -5972,7 +5184,7 @@
       </c>
       <c r="O41" s="13" t="n"/>
       <c r="P41" s="16">
-        <f>IFERROR(N41+VLOOKUP(E41,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N41+VLOOKUP(E41,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q41" s="13" t="n"/>
@@ -6022,7 +5234,7 @@
         </is>
       </c>
       <c r="D42" s="15">
-        <f>IFERROR(VLOOKUP(C42,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C42,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E42" s="14" t="inlineStr">
@@ -6031,13 +5243,10 @@
         </is>
       </c>
       <c r="F42" s="15">
-        <f>IFERROR(VLOOKUP(E42,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G42" s="15">
-        <f>IFERROR(VLOOKUP(B42&amp;"_"&amp;C42,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E42,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="13" t="n"/>
       <c r="H42" s="16">
         <f>IFERROR(VLOOKUP(B42,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -6065,7 +5274,7 @@
       </c>
       <c r="O42" s="13" t="n"/>
       <c r="P42" s="16">
-        <f>IFERROR(N42+VLOOKUP(E42,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N42+VLOOKUP(E42,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q42" s="13" t="n"/>
@@ -6111,7 +5320,7 @@
         </is>
       </c>
       <c r="D43" s="15">
-        <f>IFERROR(VLOOKUP(C43,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C43,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E43" s="14" t="inlineStr">
@@ -6120,13 +5329,10 @@
         </is>
       </c>
       <c r="F43" s="15">
-        <f>IFERROR(VLOOKUP(E43,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G43" s="15">
-        <f>IFERROR(VLOOKUP(B43&amp;"_"&amp;C43,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E43,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="13" t="n"/>
       <c r="H43" s="16">
         <f>IFERROR(VLOOKUP(B43,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -6158,7 +5364,7 @@
         <v>46147</v>
       </c>
       <c r="P43" s="16">
-        <f>IFERROR(N43+VLOOKUP(E43,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N43+VLOOKUP(E43,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q43" s="13" t="n"/>
@@ -6204,7 +5410,7 @@
         </is>
       </c>
       <c r="D44" s="15">
-        <f>IFERROR(VLOOKUP(C44,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C44,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E44" s="14" t="inlineStr">
@@ -6213,13 +5419,10 @@
         </is>
       </c>
       <c r="F44" s="15">
-        <f>IFERROR(VLOOKUP(E44,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G44" s="15">
-        <f>IFERROR(VLOOKUP(B44&amp;"_"&amp;C44,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E44,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="13" t="n"/>
       <c r="H44" s="16">
         <f>IFERROR(VLOOKUP(B44,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -6251,7 +5454,7 @@
         <v>46148</v>
       </c>
       <c r="P44" s="16">
-        <f>IFERROR(N44+VLOOKUP(E44,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N44+VLOOKUP(E44,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q44" s="20" t="n">
@@ -6299,7 +5502,7 @@
         </is>
       </c>
       <c r="D45" s="15">
-        <f>IFERROR(VLOOKUP(C45,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C45,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E45" s="14" t="inlineStr">
@@ -6308,13 +5511,10 @@
         </is>
       </c>
       <c r="F45" s="15">
-        <f>IFERROR(VLOOKUP(E45,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G45" s="15">
-        <f>IFERROR(VLOOKUP(B45&amp;"_"&amp;C45,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E45,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="13" t="n"/>
       <c r="H45" s="16">
         <f>IFERROR(VLOOKUP(B45,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -6344,7 +5544,7 @@
       </c>
       <c r="O45" s="13" t="n"/>
       <c r="P45" s="16">
-        <f>IFERROR(N45+VLOOKUP(E45,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N45+VLOOKUP(E45,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q45" s="13" t="n"/>
@@ -6390,7 +5590,7 @@
         </is>
       </c>
       <c r="D46" s="15">
-        <f>IFERROR(VLOOKUP(C46,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C46,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E46" s="14" t="inlineStr">
@@ -6399,13 +5599,10 @@
         </is>
       </c>
       <c r="F46" s="15">
-        <f>IFERROR(VLOOKUP(E46,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G46" s="15">
-        <f>IFERROR(VLOOKUP(B46&amp;"_"&amp;C46,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E46,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="13" t="n"/>
       <c r="H46" s="16">
         <f>IFERROR(VLOOKUP(B46,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -6437,7 +5634,7 @@
         <v>46144</v>
       </c>
       <c r="P46" s="16">
-        <f>IFERROR(N46+VLOOKUP(E46,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N46+VLOOKUP(E46,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q46" s="20" t="n">
@@ -6491,7 +5688,7 @@
         </is>
       </c>
       <c r="D47" s="15">
-        <f>IFERROR(VLOOKUP(C47,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C47,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E47" s="14" t="inlineStr">
@@ -6500,13 +5697,10 @@
         </is>
       </c>
       <c r="F47" s="15">
-        <f>IFERROR(VLOOKUP(E47,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G47" s="15">
-        <f>IFERROR(VLOOKUP(B47&amp;"_"&amp;C47,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E47,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="13" t="n"/>
       <c r="H47" s="16">
         <f>IFERROR(VLOOKUP(B47,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -6538,7 +5732,7 @@
         <v>46145</v>
       </c>
       <c r="P47" s="16">
-        <f>IFERROR(N47+VLOOKUP(E47,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N47+VLOOKUP(E47,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q47" s="20" t="n">
@@ -6588,7 +5782,7 @@
         </is>
       </c>
       <c r="D48" s="15">
-        <f>IFERROR(VLOOKUP(C48,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C48,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E48" s="14" t="inlineStr">
@@ -6597,13 +5791,10 @@
         </is>
       </c>
       <c r="F48" s="15">
-        <f>IFERROR(VLOOKUP(E48,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G48" s="15">
-        <f>IFERROR(VLOOKUP(B48&amp;"_"&amp;C48,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E48,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G48" s="13" t="n"/>
       <c r="H48" s="16">
         <f>IFERROR(VLOOKUP(B48,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -6635,7 +5826,7 @@
         <v>46146</v>
       </c>
       <c r="P48" s="16">
-        <f>IFERROR(N48+VLOOKUP(E48,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N48+VLOOKUP(E48,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q48" s="20" t="n">
@@ -6685,7 +5876,7 @@
         </is>
       </c>
       <c r="D49" s="15">
-        <f>IFERROR(VLOOKUP(C49,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C49,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E49" s="14" t="inlineStr">
@@ -6694,13 +5885,10 @@
         </is>
       </c>
       <c r="F49" s="15">
-        <f>IFERROR(VLOOKUP(E49,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G49" s="15">
-        <f>IFERROR(VLOOKUP(B49&amp;"_"&amp;C49,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E49,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="13" t="n"/>
       <c r="H49" s="16">
         <f>IFERROR(VLOOKUP(B49,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -6722,7 +5910,7 @@
       </c>
       <c r="O49" s="13" t="n"/>
       <c r="P49" s="16">
-        <f>IFERROR(N49+VLOOKUP(E49,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N49+VLOOKUP(E49,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q49" s="13" t="n"/>
@@ -6768,7 +5956,7 @@
         </is>
       </c>
       <c r="D50" s="15">
-        <f>IFERROR(VLOOKUP(C50,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C50,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E50" s="14" t="inlineStr">
@@ -6777,13 +5965,10 @@
         </is>
       </c>
       <c r="F50" s="15">
-        <f>IFERROR(VLOOKUP(E50,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G50" s="15">
-        <f>IFERROR(VLOOKUP(B50&amp;"_"&amp;C50,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E50,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G50" s="13" t="n"/>
       <c r="H50" s="16">
         <f>IFERROR(VLOOKUP(B50,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -6811,7 +5996,7 @@
       </c>
       <c r="O50" s="13" t="n"/>
       <c r="P50" s="16">
-        <f>IFERROR(N50+VLOOKUP(E50,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N50+VLOOKUP(E50,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q50" s="13" t="n"/>
@@ -6857,7 +6042,7 @@
         </is>
       </c>
       <c r="D51" s="15">
-        <f>IFERROR(VLOOKUP(C51,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C51,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E51" s="14" t="inlineStr">
@@ -6866,13 +6051,10 @@
         </is>
       </c>
       <c r="F51" s="15">
-        <f>IFERROR(VLOOKUP(E51,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G51" s="15">
-        <f>IFERROR(VLOOKUP(B51&amp;"_"&amp;C51,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E51,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G51" s="13" t="n"/>
       <c r="H51" s="16">
         <f>IFERROR(VLOOKUP(B51,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -6904,7 +6086,7 @@
         <v>46121</v>
       </c>
       <c r="P51" s="16">
-        <f>IFERROR(N51+VLOOKUP(E51,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N51+VLOOKUP(E51,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q51" s="13" t="n"/>
@@ -6950,7 +6132,7 @@
         </is>
       </c>
       <c r="D52" s="15">
-        <f>IFERROR(VLOOKUP(C52,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C52,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E52" s="14" t="inlineStr">
@@ -6959,13 +6141,10 @@
         </is>
       </c>
       <c r="F52" s="15">
-        <f>IFERROR(VLOOKUP(E52,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G52" s="15">
-        <f>IFERROR(VLOOKUP(B52&amp;"_"&amp;C52,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E52,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G52" s="13" t="n"/>
       <c r="H52" s="16">
         <f>IFERROR(VLOOKUP(B52,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -6997,7 +6176,7 @@
         <v>46116</v>
       </c>
       <c r="P52" s="16">
-        <f>IFERROR(N52+VLOOKUP(E52,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N52+VLOOKUP(E52,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q52" s="20" t="n">
@@ -7047,7 +6226,7 @@
         </is>
       </c>
       <c r="D53" s="15">
-        <f>IFERROR(VLOOKUP(C53,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C53,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E53" s="14" t="inlineStr">
@@ -7056,13 +6235,10 @@
         </is>
       </c>
       <c r="F53" s="15">
-        <f>IFERROR(VLOOKUP(E53,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G53" s="15">
-        <f>IFERROR(VLOOKUP(B53&amp;"_"&amp;C53,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E53,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G53" s="13" t="n"/>
       <c r="H53" s="16">
         <f>IFERROR(VLOOKUP(B53,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -7086,7 +6262,7 @@
       </c>
       <c r="O53" s="13" t="n"/>
       <c r="P53" s="16">
-        <f>IFERROR(N53+VLOOKUP(E53,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N53+VLOOKUP(E53,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q53" s="13" t="n"/>
@@ -7132,7 +6308,7 @@
         </is>
       </c>
       <c r="D54" s="15">
-        <f>IFERROR(VLOOKUP(C54,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C54,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E54" s="14" t="inlineStr">
@@ -7141,13 +6317,10 @@
         </is>
       </c>
       <c r="F54" s="15">
-        <f>IFERROR(VLOOKUP(E54,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G54" s="15">
-        <f>IFERROR(VLOOKUP(B54&amp;"_"&amp;C54,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E54,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G54" s="13" t="n"/>
       <c r="H54" s="16">
         <f>IFERROR(VLOOKUP(B54,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -7177,7 +6350,7 @@
       </c>
       <c r="O54" s="13" t="n"/>
       <c r="P54" s="16">
-        <f>IFERROR(N54+VLOOKUP(E54,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N54+VLOOKUP(E54,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q54" s="13" t="n"/>
@@ -7223,7 +6396,7 @@
         </is>
       </c>
       <c r="D55" s="15">
-        <f>IFERROR(VLOOKUP(C55,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C55,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E55" s="14" t="inlineStr">
@@ -7232,13 +6405,10 @@
         </is>
       </c>
       <c r="F55" s="15">
-        <f>IFERROR(VLOOKUP(E55,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G55" s="15">
-        <f>IFERROR(VLOOKUP(B55&amp;"_"&amp;C55,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E55,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G55" s="13" t="n"/>
       <c r="H55" s="16">
         <f>IFERROR(VLOOKUP(B55,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -7270,7 +6440,7 @@
         <v>46119</v>
       </c>
       <c r="P55" s="16">
-        <f>IFERROR(N55+VLOOKUP(E55,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N55+VLOOKUP(E55,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q55" s="20" t="n">
@@ -7320,7 +6490,7 @@
         </is>
       </c>
       <c r="D56" s="15">
-        <f>IFERROR(VLOOKUP(C56,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C56,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E56" s="14" t="inlineStr">
@@ -7329,13 +6499,10 @@
         </is>
       </c>
       <c r="F56" s="15">
-        <f>IFERROR(VLOOKUP(E56,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G56" s="15">
-        <f>IFERROR(VLOOKUP(B56&amp;"_"&amp;C56,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E56,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G56" s="13" t="n"/>
       <c r="H56" s="16">
         <f>IFERROR(VLOOKUP(B56,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -7363,7 +6530,7 @@
       </c>
       <c r="O56" s="13" t="n"/>
       <c r="P56" s="16">
-        <f>IFERROR(N56+VLOOKUP(E56,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N56+VLOOKUP(E56,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q56" s="13" t="n"/>
@@ -7409,7 +6576,7 @@
         </is>
       </c>
       <c r="D57" s="15">
-        <f>IFERROR(VLOOKUP(C57,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C57,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E57" s="14" t="inlineStr">
@@ -7418,13 +6585,10 @@
         </is>
       </c>
       <c r="F57" s="15">
-        <f>IFERROR(VLOOKUP(E57,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G57" s="15">
-        <f>IFERROR(VLOOKUP(B57&amp;"_"&amp;C57,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E57,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G57" s="13" t="n"/>
       <c r="H57" s="16">
         <f>IFERROR(VLOOKUP(B57,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -7456,7 +6620,7 @@
         <v>46121</v>
       </c>
       <c r="P57" s="16">
-        <f>IFERROR(N57+VLOOKUP(E57,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N57+VLOOKUP(E57,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q57" s="20" t="n">
@@ -7504,7 +6668,7 @@
         </is>
       </c>
       <c r="D58" s="15">
-        <f>IFERROR(VLOOKUP(C58,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C58,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E58" s="14" t="inlineStr">
@@ -7513,13 +6677,10 @@
         </is>
       </c>
       <c r="F58" s="15">
-        <f>IFERROR(VLOOKUP(E58,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G58" s="15">
-        <f>IFERROR(VLOOKUP(B58&amp;"_"&amp;C58,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E58,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G58" s="13" t="n"/>
       <c r="H58" s="16">
         <f>IFERROR(VLOOKUP(B58,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -7547,7 +6708,7 @@
       </c>
       <c r="O58" s="13" t="n"/>
       <c r="P58" s="16">
-        <f>IFERROR(N58+VLOOKUP(E58,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N58+VLOOKUP(E58,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q58" s="13" t="n"/>
@@ -7597,7 +6758,7 @@
         </is>
       </c>
       <c r="D59" s="15">
-        <f>IFERROR(VLOOKUP(C59,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C59,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E59" s="14" t="inlineStr">
@@ -7606,13 +6767,10 @@
         </is>
       </c>
       <c r="F59" s="15">
-        <f>IFERROR(VLOOKUP(E59,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G59" s="15">
-        <f>IFERROR(VLOOKUP(B59&amp;"_"&amp;C59,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E59,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G59" s="13" t="n"/>
       <c r="H59" s="16">
         <f>IFERROR(VLOOKUP(B59,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -7644,7 +6802,7 @@
         <v>46117</v>
       </c>
       <c r="P59" s="16">
-        <f>IFERROR(N59+VLOOKUP(E59,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N59+VLOOKUP(E59,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q59" s="20" t="n">
@@ -7694,7 +6852,7 @@
         </is>
       </c>
       <c r="D60" s="15">
-        <f>IFERROR(VLOOKUP(C60,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C60,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E60" s="14" t="inlineStr">
@@ -7703,13 +6861,10 @@
         </is>
       </c>
       <c r="F60" s="15">
-        <f>IFERROR(VLOOKUP(E60,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G60" s="15">
-        <f>IFERROR(VLOOKUP(B60&amp;"_"&amp;C60,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E60,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G60" s="13" t="n"/>
       <c r="H60" s="16">
         <f>IFERROR(VLOOKUP(B60,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -7737,7 +6892,7 @@
       </c>
       <c r="O60" s="13" t="n"/>
       <c r="P60" s="16">
-        <f>IFERROR(N60+VLOOKUP(E60,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N60+VLOOKUP(E60,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q60" s="13" t="n"/>
@@ -7783,7 +6938,7 @@
         </is>
       </c>
       <c r="D61" s="15">
-        <f>IFERROR(VLOOKUP(C61,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C61,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E61" s="14" t="inlineStr">
@@ -7792,13 +6947,10 @@
         </is>
       </c>
       <c r="F61" s="15">
-        <f>IFERROR(VLOOKUP(E61,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G61" s="15">
-        <f>IFERROR(VLOOKUP(B61&amp;"_"&amp;C61,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E61,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G61" s="13" t="n"/>
       <c r="H61" s="16">
         <f>IFERROR(VLOOKUP(B61,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -7830,7 +6982,7 @@
         <v>46119</v>
       </c>
       <c r="P61" s="16">
-        <f>IFERROR(N61+VLOOKUP(E61,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N61+VLOOKUP(E61,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q61" s="13" t="n"/>
@@ -7876,7 +7028,7 @@
         </is>
       </c>
       <c r="D62" s="15">
-        <f>IFERROR(VLOOKUP(C62,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C62,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E62" s="14" t="inlineStr">
@@ -7885,13 +7037,10 @@
         </is>
       </c>
       <c r="F62" s="15">
-        <f>IFERROR(VLOOKUP(E62,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G62" s="15">
-        <f>IFERROR(VLOOKUP(B62&amp;"_"&amp;C62,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E62,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G62" s="13" t="n"/>
       <c r="H62" s="16">
         <f>IFERROR(VLOOKUP(B62,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -7923,7 +7072,7 @@
         <v>46120</v>
       </c>
       <c r="P62" s="16">
-        <f>IFERROR(N62+VLOOKUP(E62,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N62+VLOOKUP(E62,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q62" s="20" t="n">
@@ -7973,7 +7122,7 @@
         </is>
       </c>
       <c r="D63" s="15">
-        <f>IFERROR(VLOOKUP(C63,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C63,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E63" s="14" t="inlineStr">
@@ -7982,13 +7131,10 @@
         </is>
       </c>
       <c r="F63" s="15">
-        <f>IFERROR(VLOOKUP(E63,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G63" s="15">
-        <f>IFERROR(VLOOKUP(B63&amp;"_"&amp;C63,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E63,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G63" s="13" t="n"/>
       <c r="H63" s="16">
         <f>IFERROR(VLOOKUP(B63,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -8018,7 +7164,7 @@
       </c>
       <c r="O63" s="13" t="n"/>
       <c r="P63" s="16">
-        <f>IFERROR(N63+VLOOKUP(E63,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N63+VLOOKUP(E63,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q63" s="13" t="n"/>
@@ -8068,7 +7214,7 @@
         </is>
       </c>
       <c r="D64" s="15">
-        <f>IFERROR(VLOOKUP(C64,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C64,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E64" s="14" t="inlineStr">
@@ -8077,13 +7223,10 @@
         </is>
       </c>
       <c r="F64" s="15">
-        <f>IFERROR(VLOOKUP(E64,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G64" s="15">
-        <f>IFERROR(VLOOKUP(B64&amp;"_"&amp;C64,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E64,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G64" s="13" t="n"/>
       <c r="H64" s="16">
         <f>IFERROR(VLOOKUP(B64,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -8111,7 +7254,7 @@
       </c>
       <c r="O64" s="13" t="n"/>
       <c r="P64" s="16">
-        <f>IFERROR(N64+VLOOKUP(E64,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N64+VLOOKUP(E64,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q64" s="13" t="n"/>
@@ -8157,7 +7300,7 @@
         </is>
       </c>
       <c r="D65" s="15">
-        <f>IFERROR(VLOOKUP(C65,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C65,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E65" s="14" t="inlineStr">
@@ -8166,13 +7309,10 @@
         </is>
       </c>
       <c r="F65" s="15">
-        <f>IFERROR(VLOOKUP(E65,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G65" s="15">
-        <f>IFERROR(VLOOKUP(B65&amp;"_"&amp;C65,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E65,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G65" s="13" t="n"/>
       <c r="H65" s="16">
         <f>IFERROR(VLOOKUP(B65,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -8204,7 +7344,7 @@
         <v>46117</v>
       </c>
       <c r="P65" s="16">
-        <f>IFERROR(N65+VLOOKUP(E65,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N65+VLOOKUP(E65,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q65" s="13" t="n"/>
@@ -8250,7 +7390,7 @@
         </is>
       </c>
       <c r="D66" s="15">
-        <f>IFERROR(VLOOKUP(C66,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C66,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E66" s="14" t="inlineStr">
@@ -8259,13 +7399,10 @@
         </is>
       </c>
       <c r="F66" s="15">
-        <f>IFERROR(VLOOKUP(E66,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G66" s="15">
-        <f>IFERROR(VLOOKUP(B66&amp;"_"&amp;C66,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E66,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G66" s="13" t="n"/>
       <c r="H66" s="16">
         <f>IFERROR(VLOOKUP(B66,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -8297,7 +7434,7 @@
         <v>46118</v>
       </c>
       <c r="P66" s="16">
-        <f>IFERROR(N66+VLOOKUP(E66,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N66+VLOOKUP(E66,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q66" s="20" t="n">
@@ -8345,7 +7482,7 @@
         </is>
       </c>
       <c r="D67" s="15">
-        <f>IFERROR(VLOOKUP(C67,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C67,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E67" s="14" t="inlineStr">
@@ -8354,13 +7491,10 @@
         </is>
       </c>
       <c r="F67" s="15">
-        <f>IFERROR(VLOOKUP(E67,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G67" s="15">
-        <f>IFERROR(VLOOKUP(B67&amp;"_"&amp;C67,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E67,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G67" s="13" t="n"/>
       <c r="H67" s="16">
         <f>IFERROR(VLOOKUP(B67,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -8390,7 +7524,7 @@
       </c>
       <c r="O67" s="13" t="n"/>
       <c r="P67" s="16">
-        <f>IFERROR(N67+VLOOKUP(E67,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N67+VLOOKUP(E67,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q67" s="13" t="n"/>
@@ -8436,7 +7570,7 @@
         </is>
       </c>
       <c r="D68" s="15">
-        <f>IFERROR(VLOOKUP(C68,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C68,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E68" s="14" t="inlineStr">
@@ -8445,13 +7579,10 @@
         </is>
       </c>
       <c r="F68" s="15">
-        <f>IFERROR(VLOOKUP(E68,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G68" s="15">
-        <f>IFERROR(VLOOKUP(B68&amp;"_"&amp;C68,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E68,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G68" s="13" t="n"/>
       <c r="H68" s="16">
         <f>IFERROR(VLOOKUP(B68,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -8483,7 +7614,7 @@
         <v>46120</v>
       </c>
       <c r="P68" s="16">
-        <f>IFERROR(N68+VLOOKUP(E68,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N68+VLOOKUP(E68,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q68" s="20" t="n">
@@ -8537,7 +7668,7 @@
         </is>
       </c>
       <c r="D69" s="15">
-        <f>IFERROR(VLOOKUP(C69,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C69,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E69" s="14" t="inlineStr">
@@ -8546,13 +7677,10 @@
         </is>
       </c>
       <c r="F69" s="15">
-        <f>IFERROR(VLOOKUP(E69,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G69" s="15">
-        <f>IFERROR(VLOOKUP(B69&amp;"_"&amp;C69,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E69,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G69" s="13" t="n"/>
       <c r="H69" s="16">
         <f>IFERROR(VLOOKUP(B69,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -8584,7 +7712,7 @@
         <v>46121</v>
       </c>
       <c r="P69" s="16">
-        <f>IFERROR(N69+VLOOKUP(E69,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N69+VLOOKUP(E69,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q69" s="20" t="n">
@@ -8634,7 +7762,7 @@
         </is>
       </c>
       <c r="D70" s="15">
-        <f>IFERROR(VLOOKUP(C70,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(C70,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),"")</f>
         <v/>
       </c>
       <c r="E70" s="14" t="inlineStr">
@@ -8643,13 +7771,10 @@
         </is>
       </c>
       <c r="F70" s="15">
-        <f>IFERROR(VLOOKUP(E70,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G70" s="15">
-        <f>IFERROR(VLOOKUP(B70&amp;"_"&amp;C70,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(VLOOKUP(E70,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G70" s="13" t="n"/>
       <c r="H70" s="16">
         <f>IFERROR(VLOOKUP(B70,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),"")</f>
         <v/>
@@ -8681,7 +7806,7 @@
         <v>46116</v>
       </c>
       <c r="P70" s="16">
-        <f>IFERROR(N70+VLOOKUP(E70,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),"")</f>
+        <f>IFERROR(N70+VLOOKUP(E70,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),"")</f>
         <v/>
       </c>
       <c r="Q70" s="20" t="n">
@@ -8724,18 +7849,15 @@
       <c r="B71" s="13" t="n"/>
       <c r="C71" s="14" t="n"/>
       <c r="D71" s="15">
-        <f>IF(B71="","",IFERROR(VLOOKUP(C71,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B71="","",IFERROR(VLOOKUP(C71,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E71" s="14" t="n"/>
       <c r="F71" s="15">
-        <f>IF(B71="","",IFERROR(VLOOKUP(E71,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G71" s="15">
-        <f>IF(B71="","",IFERROR(VLOOKUP(B71&amp;"_"&amp;C71,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B71="","",IFERROR(VLOOKUP(E71,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G71" s="13" t="n"/>
       <c r="H71" s="16">
         <f>IF(B71="","",IFERROR(VLOOKUP(B71,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -8757,7 +7879,7 @@
       </c>
       <c r="O71" s="20" t="n"/>
       <c r="P71" s="16">
-        <f>IF(B71="","",IFERROR(N71+VLOOKUP(E71,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B71="","",IFERROR(N71+VLOOKUP(E71,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q71" s="20" t="n"/>
@@ -8796,18 +7918,15 @@
       <c r="B72" s="13" t="n"/>
       <c r="C72" s="14" t="n"/>
       <c r="D72" s="15">
-        <f>IF(B72="","",IFERROR(VLOOKUP(C72,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B72="","",IFERROR(VLOOKUP(C72,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E72" s="14" t="n"/>
       <c r="F72" s="15">
-        <f>IF(B72="","",IFERROR(VLOOKUP(E72,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G72" s="15">
-        <f>IF(B72="","",IFERROR(VLOOKUP(B72&amp;"_"&amp;C72,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B72="","",IFERROR(VLOOKUP(E72,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G72" s="13" t="n"/>
       <c r="H72" s="16">
         <f>IF(B72="","",IFERROR(VLOOKUP(B72,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -8829,7 +7948,7 @@
       </c>
       <c r="O72" s="20" t="n"/>
       <c r="P72" s="16">
-        <f>IF(B72="","",IFERROR(N72+VLOOKUP(E72,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B72="","",IFERROR(N72+VLOOKUP(E72,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q72" s="20" t="n"/>
@@ -8868,18 +7987,15 @@
       <c r="B73" s="13" t="n"/>
       <c r="C73" s="14" t="n"/>
       <c r="D73" s="15">
-        <f>IF(B73="","",IFERROR(VLOOKUP(C73,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B73="","",IFERROR(VLOOKUP(C73,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E73" s="14" t="n"/>
       <c r="F73" s="15">
-        <f>IF(B73="","",IFERROR(VLOOKUP(E73,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G73" s="15">
-        <f>IF(B73="","",IFERROR(VLOOKUP(B73&amp;"_"&amp;C73,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B73="","",IFERROR(VLOOKUP(E73,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G73" s="13" t="n"/>
       <c r="H73" s="16">
         <f>IF(B73="","",IFERROR(VLOOKUP(B73,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -8901,7 +8017,7 @@
       </c>
       <c r="O73" s="20" t="n"/>
       <c r="P73" s="16">
-        <f>IF(B73="","",IFERROR(N73+VLOOKUP(E73,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B73="","",IFERROR(N73+VLOOKUP(E73,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q73" s="20" t="n"/>
@@ -8940,18 +8056,15 @@
       <c r="B74" s="13" t="n"/>
       <c r="C74" s="14" t="n"/>
       <c r="D74" s="15">
-        <f>IF(B74="","",IFERROR(VLOOKUP(C74,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B74="","",IFERROR(VLOOKUP(C74,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E74" s="14" t="n"/>
       <c r="F74" s="15">
-        <f>IF(B74="","",IFERROR(VLOOKUP(E74,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G74" s="15">
-        <f>IF(B74="","",IFERROR(VLOOKUP(B74&amp;"_"&amp;C74,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B74="","",IFERROR(VLOOKUP(E74,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G74" s="13" t="n"/>
       <c r="H74" s="16">
         <f>IF(B74="","",IFERROR(VLOOKUP(B74,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -8973,7 +8086,7 @@
       </c>
       <c r="O74" s="20" t="n"/>
       <c r="P74" s="16">
-        <f>IF(B74="","",IFERROR(N74+VLOOKUP(E74,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B74="","",IFERROR(N74+VLOOKUP(E74,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q74" s="20" t="n"/>
@@ -9012,18 +8125,15 @@
       <c r="B75" s="13" t="n"/>
       <c r="C75" s="14" t="n"/>
       <c r="D75" s="15">
-        <f>IF(B75="","",IFERROR(VLOOKUP(C75,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B75="","",IFERROR(VLOOKUP(C75,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E75" s="14" t="n"/>
       <c r="F75" s="15">
-        <f>IF(B75="","",IFERROR(VLOOKUP(E75,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G75" s="15">
-        <f>IF(B75="","",IFERROR(VLOOKUP(B75&amp;"_"&amp;C75,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B75="","",IFERROR(VLOOKUP(E75,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G75" s="13" t="n"/>
       <c r="H75" s="16">
         <f>IF(B75="","",IFERROR(VLOOKUP(B75,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -9045,7 +8155,7 @@
       </c>
       <c r="O75" s="20" t="n"/>
       <c r="P75" s="16">
-        <f>IF(B75="","",IFERROR(N75+VLOOKUP(E75,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B75="","",IFERROR(N75+VLOOKUP(E75,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q75" s="20" t="n"/>
@@ -9084,18 +8194,15 @@
       <c r="B76" s="13" t="n"/>
       <c r="C76" s="14" t="n"/>
       <c r="D76" s="15">
-        <f>IF(B76="","",IFERROR(VLOOKUP(C76,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B76="","",IFERROR(VLOOKUP(C76,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E76" s="14" t="n"/>
       <c r="F76" s="15">
-        <f>IF(B76="","",IFERROR(VLOOKUP(E76,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G76" s="15">
-        <f>IF(B76="","",IFERROR(VLOOKUP(B76&amp;"_"&amp;C76,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B76="","",IFERROR(VLOOKUP(E76,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G76" s="13" t="n"/>
       <c r="H76" s="16">
         <f>IF(B76="","",IFERROR(VLOOKUP(B76,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -9117,7 +8224,7 @@
       </c>
       <c r="O76" s="20" t="n"/>
       <c r="P76" s="16">
-        <f>IF(B76="","",IFERROR(N76+VLOOKUP(E76,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B76="","",IFERROR(N76+VLOOKUP(E76,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q76" s="20" t="n"/>
@@ -9156,18 +8263,15 @@
       <c r="B77" s="13" t="n"/>
       <c r="C77" s="14" t="n"/>
       <c r="D77" s="15">
-        <f>IF(B77="","",IFERROR(VLOOKUP(C77,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B77="","",IFERROR(VLOOKUP(C77,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E77" s="14" t="n"/>
       <c r="F77" s="15">
-        <f>IF(B77="","",IFERROR(VLOOKUP(E77,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G77" s="15">
-        <f>IF(B77="","",IFERROR(VLOOKUP(B77&amp;"_"&amp;C77,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B77="","",IFERROR(VLOOKUP(E77,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G77" s="13" t="n"/>
       <c r="H77" s="16">
         <f>IF(B77="","",IFERROR(VLOOKUP(B77,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -9189,7 +8293,7 @@
       </c>
       <c r="O77" s="20" t="n"/>
       <c r="P77" s="16">
-        <f>IF(B77="","",IFERROR(N77+VLOOKUP(E77,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B77="","",IFERROR(N77+VLOOKUP(E77,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q77" s="20" t="n"/>
@@ -9228,18 +8332,15 @@
       <c r="B78" s="13" t="n"/>
       <c r="C78" s="14" t="n"/>
       <c r="D78" s="15">
-        <f>IF(B78="","",IFERROR(VLOOKUP(C78,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B78="","",IFERROR(VLOOKUP(C78,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E78" s="14" t="n"/>
       <c r="F78" s="15">
-        <f>IF(B78="","",IFERROR(VLOOKUP(E78,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G78" s="15">
-        <f>IF(B78="","",IFERROR(VLOOKUP(B78&amp;"_"&amp;C78,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B78="","",IFERROR(VLOOKUP(E78,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G78" s="13" t="n"/>
       <c r="H78" s="16">
         <f>IF(B78="","",IFERROR(VLOOKUP(B78,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -9261,7 +8362,7 @@
       </c>
       <c r="O78" s="20" t="n"/>
       <c r="P78" s="16">
-        <f>IF(B78="","",IFERROR(N78+VLOOKUP(E78,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B78="","",IFERROR(N78+VLOOKUP(E78,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q78" s="20" t="n"/>
@@ -9300,18 +8401,15 @@
       <c r="B79" s="13" t="n"/>
       <c r="C79" s="14" t="n"/>
       <c r="D79" s="15">
-        <f>IF(B79="","",IFERROR(VLOOKUP(C79,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B79="","",IFERROR(VLOOKUP(C79,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E79" s="14" t="n"/>
       <c r="F79" s="15">
-        <f>IF(B79="","",IFERROR(VLOOKUP(E79,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G79" s="15">
-        <f>IF(B79="","",IFERROR(VLOOKUP(B79&amp;"_"&amp;C79,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B79="","",IFERROR(VLOOKUP(E79,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G79" s="13" t="n"/>
       <c r="H79" s="16">
         <f>IF(B79="","",IFERROR(VLOOKUP(B79,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -9333,7 +8431,7 @@
       </c>
       <c r="O79" s="20" t="n"/>
       <c r="P79" s="16">
-        <f>IF(B79="","",IFERROR(N79+VLOOKUP(E79,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B79="","",IFERROR(N79+VLOOKUP(E79,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q79" s="20" t="n"/>
@@ -9372,18 +8470,15 @@
       <c r="B80" s="13" t="n"/>
       <c r="C80" s="14" t="n"/>
       <c r="D80" s="15">
-        <f>IF(B80="","",IFERROR(VLOOKUP(C80,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B80="","",IFERROR(VLOOKUP(C80,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E80" s="14" t="n"/>
       <c r="F80" s="15">
-        <f>IF(B80="","",IFERROR(VLOOKUP(E80,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G80" s="15">
-        <f>IF(B80="","",IFERROR(VLOOKUP(B80&amp;"_"&amp;C80,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B80="","",IFERROR(VLOOKUP(E80,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G80" s="13" t="n"/>
       <c r="H80" s="16">
         <f>IF(B80="","",IFERROR(VLOOKUP(B80,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -9405,7 +8500,7 @@
       </c>
       <c r="O80" s="20" t="n"/>
       <c r="P80" s="16">
-        <f>IF(B80="","",IFERROR(N80+VLOOKUP(E80,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B80="","",IFERROR(N80+VLOOKUP(E80,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q80" s="20" t="n"/>
@@ -9444,18 +8539,15 @@
       <c r="B81" s="13" t="n"/>
       <c r="C81" s="14" t="n"/>
       <c r="D81" s="15">
-        <f>IF(B81="","",IFERROR(VLOOKUP(C81,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B81="","",IFERROR(VLOOKUP(C81,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E81" s="14" t="n"/>
       <c r="F81" s="15">
-        <f>IF(B81="","",IFERROR(VLOOKUP(E81,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G81" s="15">
-        <f>IF(B81="","",IFERROR(VLOOKUP(B81&amp;"_"&amp;C81,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B81="","",IFERROR(VLOOKUP(E81,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G81" s="13" t="n"/>
       <c r="H81" s="16">
         <f>IF(B81="","",IFERROR(VLOOKUP(B81,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -9477,7 +8569,7 @@
       </c>
       <c r="O81" s="20" t="n"/>
       <c r="P81" s="16">
-        <f>IF(B81="","",IFERROR(N81+VLOOKUP(E81,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B81="","",IFERROR(N81+VLOOKUP(E81,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q81" s="20" t="n"/>
@@ -9516,18 +8608,15 @@
       <c r="B82" s="13" t="n"/>
       <c r="C82" s="14" t="n"/>
       <c r="D82" s="15">
-        <f>IF(B82="","",IFERROR(VLOOKUP(C82,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B82="","",IFERROR(VLOOKUP(C82,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E82" s="14" t="n"/>
       <c r="F82" s="15">
-        <f>IF(B82="","",IFERROR(VLOOKUP(E82,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G82" s="15">
-        <f>IF(B82="","",IFERROR(VLOOKUP(B82&amp;"_"&amp;C82,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B82="","",IFERROR(VLOOKUP(E82,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G82" s="13" t="n"/>
       <c r="H82" s="16">
         <f>IF(B82="","",IFERROR(VLOOKUP(B82,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -9549,7 +8638,7 @@
       </c>
       <c r="O82" s="20" t="n"/>
       <c r="P82" s="16">
-        <f>IF(B82="","",IFERROR(N82+VLOOKUP(E82,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B82="","",IFERROR(N82+VLOOKUP(E82,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q82" s="20" t="n"/>
@@ -9588,18 +8677,15 @@
       <c r="B83" s="13" t="n"/>
       <c r="C83" s="14" t="n"/>
       <c r="D83" s="15">
-        <f>IF(B83="","",IFERROR(VLOOKUP(C83,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B83="","",IFERROR(VLOOKUP(C83,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E83" s="14" t="n"/>
       <c r="F83" s="15">
-        <f>IF(B83="","",IFERROR(VLOOKUP(E83,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G83" s="15">
-        <f>IF(B83="","",IFERROR(VLOOKUP(B83&amp;"_"&amp;C83,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B83="","",IFERROR(VLOOKUP(E83,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G83" s="13" t="n"/>
       <c r="H83" s="16">
         <f>IF(B83="","",IFERROR(VLOOKUP(B83,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -9621,7 +8707,7 @@
       </c>
       <c r="O83" s="20" t="n"/>
       <c r="P83" s="16">
-        <f>IF(B83="","",IFERROR(N83+VLOOKUP(E83,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B83="","",IFERROR(N83+VLOOKUP(E83,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q83" s="20" t="n"/>
@@ -9660,18 +8746,15 @@
       <c r="B84" s="13" t="n"/>
       <c r="C84" s="14" t="n"/>
       <c r="D84" s="15">
-        <f>IF(B84="","",IFERROR(VLOOKUP(C84,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B84="","",IFERROR(VLOOKUP(C84,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E84" s="14" t="n"/>
       <c r="F84" s="15">
-        <f>IF(B84="","",IFERROR(VLOOKUP(E84,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G84" s="15">
-        <f>IF(B84="","",IFERROR(VLOOKUP(B84&amp;"_"&amp;C84,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B84="","",IFERROR(VLOOKUP(E84,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G84" s="13" t="n"/>
       <c r="H84" s="16">
         <f>IF(B84="","",IFERROR(VLOOKUP(B84,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -9693,7 +8776,7 @@
       </c>
       <c r="O84" s="20" t="n"/>
       <c r="P84" s="16">
-        <f>IF(B84="","",IFERROR(N84+VLOOKUP(E84,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B84="","",IFERROR(N84+VLOOKUP(E84,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q84" s="20" t="n"/>
@@ -9732,18 +8815,15 @@
       <c r="B85" s="13" t="n"/>
       <c r="C85" s="14" t="n"/>
       <c r="D85" s="15">
-        <f>IF(B85="","",IFERROR(VLOOKUP(C85,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B85="","",IFERROR(VLOOKUP(C85,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E85" s="14" t="n"/>
       <c r="F85" s="15">
-        <f>IF(B85="","",IFERROR(VLOOKUP(E85,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G85" s="15">
-        <f>IF(B85="","",IFERROR(VLOOKUP(B85&amp;"_"&amp;C85,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B85="","",IFERROR(VLOOKUP(E85,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G85" s="13" t="n"/>
       <c r="H85" s="16">
         <f>IF(B85="","",IFERROR(VLOOKUP(B85,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -9765,7 +8845,7 @@
       </c>
       <c r="O85" s="20" t="n"/>
       <c r="P85" s="16">
-        <f>IF(B85="","",IFERROR(N85+VLOOKUP(E85,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B85="","",IFERROR(N85+VLOOKUP(E85,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q85" s="20" t="n"/>
@@ -9804,18 +8884,15 @@
       <c r="B86" s="13" t="n"/>
       <c r="C86" s="14" t="n"/>
       <c r="D86" s="15">
-        <f>IF(B86="","",IFERROR(VLOOKUP(C86,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B86="","",IFERROR(VLOOKUP(C86,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E86" s="14" t="n"/>
       <c r="F86" s="15">
-        <f>IF(B86="","",IFERROR(VLOOKUP(E86,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G86" s="15">
-        <f>IF(B86="","",IFERROR(VLOOKUP(B86&amp;"_"&amp;C86,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B86="","",IFERROR(VLOOKUP(E86,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G86" s="13" t="n"/>
       <c r="H86" s="16">
         <f>IF(B86="","",IFERROR(VLOOKUP(B86,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -9837,7 +8914,7 @@
       </c>
       <c r="O86" s="20" t="n"/>
       <c r="P86" s="16">
-        <f>IF(B86="","",IFERROR(N86+VLOOKUP(E86,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B86="","",IFERROR(N86+VLOOKUP(E86,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q86" s="20" t="n"/>
@@ -9876,18 +8953,15 @@
       <c r="B87" s="13" t="n"/>
       <c r="C87" s="14" t="n"/>
       <c r="D87" s="15">
-        <f>IF(B87="","",IFERROR(VLOOKUP(C87,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B87="","",IFERROR(VLOOKUP(C87,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E87" s="14" t="n"/>
       <c r="F87" s="15">
-        <f>IF(B87="","",IFERROR(VLOOKUP(E87,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G87" s="15">
-        <f>IF(B87="","",IFERROR(VLOOKUP(B87&amp;"_"&amp;C87,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B87="","",IFERROR(VLOOKUP(E87,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G87" s="13" t="n"/>
       <c r="H87" s="16">
         <f>IF(B87="","",IFERROR(VLOOKUP(B87,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -9909,7 +8983,7 @@
       </c>
       <c r="O87" s="20" t="n"/>
       <c r="P87" s="16">
-        <f>IF(B87="","",IFERROR(N87+VLOOKUP(E87,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B87="","",IFERROR(N87+VLOOKUP(E87,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q87" s="20" t="n"/>
@@ -9948,18 +9022,15 @@
       <c r="B88" s="13" t="n"/>
       <c r="C88" s="14" t="n"/>
       <c r="D88" s="15">
-        <f>IF(B88="","",IFERROR(VLOOKUP(C88,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B88="","",IFERROR(VLOOKUP(C88,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E88" s="14" t="n"/>
       <c r="F88" s="15">
-        <f>IF(B88="","",IFERROR(VLOOKUP(E88,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G88" s="15">
-        <f>IF(B88="","",IFERROR(VLOOKUP(B88&amp;"_"&amp;C88,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B88="","",IFERROR(VLOOKUP(E88,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G88" s="13" t="n"/>
       <c r="H88" s="16">
         <f>IF(B88="","",IFERROR(VLOOKUP(B88,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -9981,7 +9052,7 @@
       </c>
       <c r="O88" s="20" t="n"/>
       <c r="P88" s="16">
-        <f>IF(B88="","",IFERROR(N88+VLOOKUP(E88,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B88="","",IFERROR(N88+VLOOKUP(E88,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q88" s="20" t="n"/>
@@ -10020,18 +9091,15 @@
       <c r="B89" s="13" t="n"/>
       <c r="C89" s="14" t="n"/>
       <c r="D89" s="15">
-        <f>IF(B89="","",IFERROR(VLOOKUP(C89,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B89="","",IFERROR(VLOOKUP(C89,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E89" s="14" t="n"/>
       <c r="F89" s="15">
-        <f>IF(B89="","",IFERROR(VLOOKUP(E89,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G89" s="15">
-        <f>IF(B89="","",IFERROR(VLOOKUP(B89&amp;"_"&amp;C89,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B89="","",IFERROR(VLOOKUP(E89,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G89" s="13" t="n"/>
       <c r="H89" s="16">
         <f>IF(B89="","",IFERROR(VLOOKUP(B89,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -10053,7 +9121,7 @@
       </c>
       <c r="O89" s="20" t="n"/>
       <c r="P89" s="16">
-        <f>IF(B89="","",IFERROR(N89+VLOOKUP(E89,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B89="","",IFERROR(N89+VLOOKUP(E89,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q89" s="20" t="n"/>
@@ -10092,18 +9160,15 @@
       <c r="B90" s="13" t="n"/>
       <c r="C90" s="14" t="n"/>
       <c r="D90" s="15">
-        <f>IF(B90="","",IFERROR(VLOOKUP(C90,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B90="","",IFERROR(VLOOKUP(C90,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E90" s="14" t="n"/>
       <c r="F90" s="15">
-        <f>IF(B90="","",IFERROR(VLOOKUP(E90,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G90" s="15">
-        <f>IF(B90="","",IFERROR(VLOOKUP(B90&amp;"_"&amp;C90,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B90="","",IFERROR(VLOOKUP(E90,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G90" s="13" t="n"/>
       <c r="H90" s="16">
         <f>IF(B90="","",IFERROR(VLOOKUP(B90,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -10125,7 +9190,7 @@
       </c>
       <c r="O90" s="20" t="n"/>
       <c r="P90" s="16">
-        <f>IF(B90="","",IFERROR(N90+VLOOKUP(E90,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B90="","",IFERROR(N90+VLOOKUP(E90,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q90" s="20" t="n"/>
@@ -10164,18 +9229,15 @@
       <c r="B91" s="13" t="n"/>
       <c r="C91" s="14" t="n"/>
       <c r="D91" s="15">
-        <f>IF(B91="","",IFERROR(VLOOKUP(C91,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B91="","",IFERROR(VLOOKUP(C91,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E91" s="14" t="n"/>
       <c r="F91" s="15">
-        <f>IF(B91="","",IFERROR(VLOOKUP(E91,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G91" s="15">
-        <f>IF(B91="","",IFERROR(VLOOKUP(B91&amp;"_"&amp;C91,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B91="","",IFERROR(VLOOKUP(E91,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G91" s="13" t="n"/>
       <c r="H91" s="16">
         <f>IF(B91="","",IFERROR(VLOOKUP(B91,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -10197,7 +9259,7 @@
       </c>
       <c r="O91" s="20" t="n"/>
       <c r="P91" s="16">
-        <f>IF(B91="","",IFERROR(N91+VLOOKUP(E91,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B91="","",IFERROR(N91+VLOOKUP(E91,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q91" s="20" t="n"/>
@@ -10236,18 +9298,15 @@
       <c r="B92" s="13" t="n"/>
       <c r="C92" s="14" t="n"/>
       <c r="D92" s="15">
-        <f>IF(B92="","",IFERROR(VLOOKUP(C92,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B92="","",IFERROR(VLOOKUP(C92,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E92" s="14" t="n"/>
       <c r="F92" s="15">
-        <f>IF(B92="","",IFERROR(VLOOKUP(E92,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G92" s="15">
-        <f>IF(B92="","",IFERROR(VLOOKUP(B92&amp;"_"&amp;C92,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B92="","",IFERROR(VLOOKUP(E92,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G92" s="13" t="n"/>
       <c r="H92" s="16">
         <f>IF(B92="","",IFERROR(VLOOKUP(B92,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -10269,7 +9328,7 @@
       </c>
       <c r="O92" s="20" t="n"/>
       <c r="P92" s="16">
-        <f>IF(B92="","",IFERROR(N92+VLOOKUP(E92,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B92="","",IFERROR(N92+VLOOKUP(E92,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q92" s="20" t="n"/>
@@ -10308,18 +9367,15 @@
       <c r="B93" s="13" t="n"/>
       <c r="C93" s="14" t="n"/>
       <c r="D93" s="15">
-        <f>IF(B93="","",IFERROR(VLOOKUP(C93,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B93="","",IFERROR(VLOOKUP(C93,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E93" s="14" t="n"/>
       <c r="F93" s="15">
-        <f>IF(B93="","",IFERROR(VLOOKUP(E93,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G93" s="15">
-        <f>IF(B93="","",IFERROR(VLOOKUP(B93&amp;"_"&amp;C93,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B93="","",IFERROR(VLOOKUP(E93,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G93" s="13" t="n"/>
       <c r="H93" s="16">
         <f>IF(B93="","",IFERROR(VLOOKUP(B93,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -10341,7 +9397,7 @@
       </c>
       <c r="O93" s="20" t="n"/>
       <c r="P93" s="16">
-        <f>IF(B93="","",IFERROR(N93+VLOOKUP(E93,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B93="","",IFERROR(N93+VLOOKUP(E93,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q93" s="20" t="n"/>
@@ -10380,18 +9436,15 @@
       <c r="B94" s="13" t="n"/>
       <c r="C94" s="14" t="n"/>
       <c r="D94" s="15">
-        <f>IF(B94="","",IFERROR(VLOOKUP(C94,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B94="","",IFERROR(VLOOKUP(C94,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E94" s="14" t="n"/>
       <c r="F94" s="15">
-        <f>IF(B94="","",IFERROR(VLOOKUP(E94,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G94" s="15">
-        <f>IF(B94="","",IFERROR(VLOOKUP(B94&amp;"_"&amp;C94,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B94="","",IFERROR(VLOOKUP(E94,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G94" s="13" t="n"/>
       <c r="H94" s="16">
         <f>IF(B94="","",IFERROR(VLOOKUP(B94,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -10413,7 +9466,7 @@
       </c>
       <c r="O94" s="20" t="n"/>
       <c r="P94" s="16">
-        <f>IF(B94="","",IFERROR(N94+VLOOKUP(E94,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B94="","",IFERROR(N94+VLOOKUP(E94,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q94" s="20" t="n"/>
@@ -10452,18 +9505,15 @@
       <c r="B95" s="13" t="n"/>
       <c r="C95" s="14" t="n"/>
       <c r="D95" s="15">
-        <f>IF(B95="","",IFERROR(VLOOKUP(C95,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B95="","",IFERROR(VLOOKUP(C95,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E95" s="14" t="n"/>
       <c r="F95" s="15">
-        <f>IF(B95="","",IFERROR(VLOOKUP(E95,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G95" s="15">
-        <f>IF(B95="","",IFERROR(VLOOKUP(B95&amp;"_"&amp;C95,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B95="","",IFERROR(VLOOKUP(E95,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G95" s="13" t="n"/>
       <c r="H95" s="16">
         <f>IF(B95="","",IFERROR(VLOOKUP(B95,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -10485,7 +9535,7 @@
       </c>
       <c r="O95" s="20" t="n"/>
       <c r="P95" s="16">
-        <f>IF(B95="","",IFERROR(N95+VLOOKUP(E95,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B95="","",IFERROR(N95+VLOOKUP(E95,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q95" s="20" t="n"/>
@@ -10524,18 +9574,15 @@
       <c r="B96" s="13" t="n"/>
       <c r="C96" s="14" t="n"/>
       <c r="D96" s="15">
-        <f>IF(B96="","",IFERROR(VLOOKUP(C96,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B96="","",IFERROR(VLOOKUP(C96,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E96" s="14" t="n"/>
       <c r="F96" s="15">
-        <f>IF(B96="","",IFERROR(VLOOKUP(E96,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G96" s="15">
-        <f>IF(B96="","",IFERROR(VLOOKUP(B96&amp;"_"&amp;C96,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B96="","",IFERROR(VLOOKUP(E96,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G96" s="13" t="n"/>
       <c r="H96" s="16">
         <f>IF(B96="","",IFERROR(VLOOKUP(B96,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -10557,7 +9604,7 @@
       </c>
       <c r="O96" s="20" t="n"/>
       <c r="P96" s="16">
-        <f>IF(B96="","",IFERROR(N96+VLOOKUP(E96,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B96="","",IFERROR(N96+VLOOKUP(E96,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q96" s="20" t="n"/>
@@ -10596,18 +9643,15 @@
       <c r="B97" s="13" t="n"/>
       <c r="C97" s="14" t="n"/>
       <c r="D97" s="15">
-        <f>IF(B97="","",IFERROR(VLOOKUP(C97,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B97="","",IFERROR(VLOOKUP(C97,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E97" s="14" t="n"/>
       <c r="F97" s="15">
-        <f>IF(B97="","",IFERROR(VLOOKUP(E97,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G97" s="15">
-        <f>IF(B97="","",IFERROR(VLOOKUP(B97&amp;"_"&amp;C97,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B97="","",IFERROR(VLOOKUP(E97,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G97" s="13" t="n"/>
       <c r="H97" s="16">
         <f>IF(B97="","",IFERROR(VLOOKUP(B97,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -10629,7 +9673,7 @@
       </c>
       <c r="O97" s="20" t="n"/>
       <c r="P97" s="16">
-        <f>IF(B97="","",IFERROR(N97+VLOOKUP(E97,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B97="","",IFERROR(N97+VLOOKUP(E97,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q97" s="20" t="n"/>
@@ -10668,18 +9712,15 @@
       <c r="B98" s="13" t="n"/>
       <c r="C98" s="14" t="n"/>
       <c r="D98" s="15">
-        <f>IF(B98="","",IFERROR(VLOOKUP(C98,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B98="","",IFERROR(VLOOKUP(C98,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E98" s="14" t="n"/>
       <c r="F98" s="15">
-        <f>IF(B98="","",IFERROR(VLOOKUP(E98,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G98" s="15">
-        <f>IF(B98="","",IFERROR(VLOOKUP(B98&amp;"_"&amp;C98,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B98="","",IFERROR(VLOOKUP(E98,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G98" s="13" t="n"/>
       <c r="H98" s="16">
         <f>IF(B98="","",IFERROR(VLOOKUP(B98,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -10701,7 +9742,7 @@
       </c>
       <c r="O98" s="20" t="n"/>
       <c r="P98" s="16">
-        <f>IF(B98="","",IFERROR(N98+VLOOKUP(E98,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B98="","",IFERROR(N98+VLOOKUP(E98,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q98" s="20" t="n"/>
@@ -10740,18 +9781,15 @@
       <c r="B99" s="13" t="n"/>
       <c r="C99" s="14" t="n"/>
       <c r="D99" s="15">
-        <f>IF(B99="","",IFERROR(VLOOKUP(C99,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B99="","",IFERROR(VLOOKUP(C99,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E99" s="14" t="n"/>
       <c r="F99" s="15">
-        <f>IF(B99="","",IFERROR(VLOOKUP(E99,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G99" s="15">
-        <f>IF(B99="","",IFERROR(VLOOKUP(B99&amp;"_"&amp;C99,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B99="","",IFERROR(VLOOKUP(E99,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G99" s="13" t="n"/>
       <c r="H99" s="16">
         <f>IF(B99="","",IFERROR(VLOOKUP(B99,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -10773,7 +9811,7 @@
       </c>
       <c r="O99" s="20" t="n"/>
       <c r="P99" s="16">
-        <f>IF(B99="","",IFERROR(N99+VLOOKUP(E99,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B99="","",IFERROR(N99+VLOOKUP(E99,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q99" s="20" t="n"/>
@@ -10812,18 +9850,15 @@
       <c r="B100" s="13" t="n"/>
       <c r="C100" s="14" t="n"/>
       <c r="D100" s="15">
-        <f>IF(B100="","",IFERROR(VLOOKUP(C100,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B100="","",IFERROR(VLOOKUP(C100,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E100" s="14" t="n"/>
       <c r="F100" s="15">
-        <f>IF(B100="","",IFERROR(VLOOKUP(E100,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G100" s="15">
-        <f>IF(B100="","",IFERROR(VLOOKUP(B100&amp;"_"&amp;C100,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B100="","",IFERROR(VLOOKUP(E100,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G100" s="13" t="n"/>
       <c r="H100" s="16">
         <f>IF(B100="","",IFERROR(VLOOKUP(B100,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -10845,7 +9880,7 @@
       </c>
       <c r="O100" s="20" t="n"/>
       <c r="P100" s="16">
-        <f>IF(B100="","",IFERROR(N100+VLOOKUP(E100,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B100="","",IFERROR(N100+VLOOKUP(E100,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q100" s="20" t="n"/>
@@ -10884,18 +9919,15 @@
       <c r="B101" s="13" t="n"/>
       <c r="C101" s="14" t="n"/>
       <c r="D101" s="15">
-        <f>IF(B101="","",IFERROR(VLOOKUP(C101,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B101="","",IFERROR(VLOOKUP(C101,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E101" s="14" t="n"/>
       <c r="F101" s="15">
-        <f>IF(B101="","",IFERROR(VLOOKUP(E101,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G101" s="15">
-        <f>IF(B101="","",IFERROR(VLOOKUP(B101&amp;"_"&amp;C101,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B101="","",IFERROR(VLOOKUP(E101,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G101" s="13" t="n"/>
       <c r="H101" s="16">
         <f>IF(B101="","",IFERROR(VLOOKUP(B101,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -10917,7 +9949,7 @@
       </c>
       <c r="O101" s="20" t="n"/>
       <c r="P101" s="16">
-        <f>IF(B101="","",IFERROR(N101+VLOOKUP(E101,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B101="","",IFERROR(N101+VLOOKUP(E101,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q101" s="20" t="n"/>
@@ -10956,18 +9988,15 @@
       <c r="B102" s="13" t="n"/>
       <c r="C102" s="14" t="n"/>
       <c r="D102" s="15">
-        <f>IF(B102="","",IFERROR(VLOOKUP(C102,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B102="","",IFERROR(VLOOKUP(C102,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E102" s="14" t="n"/>
       <c r="F102" s="15">
-        <f>IF(B102="","",IFERROR(VLOOKUP(E102,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G102" s="15">
-        <f>IF(B102="","",IFERROR(VLOOKUP(B102&amp;"_"&amp;C102,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B102="","",IFERROR(VLOOKUP(E102,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G102" s="13" t="n"/>
       <c r="H102" s="16">
         <f>IF(B102="","",IFERROR(VLOOKUP(B102,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -10989,7 +10018,7 @@
       </c>
       <c r="O102" s="20" t="n"/>
       <c r="P102" s="16">
-        <f>IF(B102="","",IFERROR(N102+VLOOKUP(E102,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B102="","",IFERROR(N102+VLOOKUP(E102,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q102" s="20" t="n"/>
@@ -11028,18 +10057,15 @@
       <c r="B103" s="13" t="n"/>
       <c r="C103" s="14" t="n"/>
       <c r="D103" s="15">
-        <f>IF(B103="","",IFERROR(VLOOKUP(C103,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B103="","",IFERROR(VLOOKUP(C103,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E103" s="14" t="n"/>
       <c r="F103" s="15">
-        <f>IF(B103="","",IFERROR(VLOOKUP(E103,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G103" s="15">
-        <f>IF(B103="","",IFERROR(VLOOKUP(B103&amp;"_"&amp;C103,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B103="","",IFERROR(VLOOKUP(E103,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G103" s="13" t="n"/>
       <c r="H103" s="16">
         <f>IF(B103="","",IFERROR(VLOOKUP(B103,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -11061,7 +10087,7 @@
       </c>
       <c r="O103" s="20" t="n"/>
       <c r="P103" s="16">
-        <f>IF(B103="","",IFERROR(N103+VLOOKUP(E103,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B103="","",IFERROR(N103+VLOOKUP(E103,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q103" s="20" t="n"/>
@@ -11100,18 +10126,15 @@
       <c r="B104" s="13" t="n"/>
       <c r="C104" s="14" t="n"/>
       <c r="D104" s="15">
-        <f>IF(B104="","",IFERROR(VLOOKUP(C104,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B104="","",IFERROR(VLOOKUP(C104,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E104" s="14" t="n"/>
       <c r="F104" s="15">
-        <f>IF(B104="","",IFERROR(VLOOKUP(E104,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G104" s="15">
-        <f>IF(B104="","",IFERROR(VLOOKUP(B104&amp;"_"&amp;C104,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B104="","",IFERROR(VLOOKUP(E104,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G104" s="13" t="n"/>
       <c r="H104" s="16">
         <f>IF(B104="","",IFERROR(VLOOKUP(B104,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -11133,7 +10156,7 @@
       </c>
       <c r="O104" s="20" t="n"/>
       <c r="P104" s="16">
-        <f>IF(B104="","",IFERROR(N104+VLOOKUP(E104,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B104="","",IFERROR(N104+VLOOKUP(E104,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q104" s="20" t="n"/>
@@ -11172,18 +10195,15 @@
       <c r="B105" s="13" t="n"/>
       <c r="C105" s="14" t="n"/>
       <c r="D105" s="15">
-        <f>IF(B105="","",IFERROR(VLOOKUP(C105,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B105="","",IFERROR(VLOOKUP(C105,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E105" s="14" t="n"/>
       <c r="F105" s="15">
-        <f>IF(B105="","",IFERROR(VLOOKUP(E105,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G105" s="15">
-        <f>IF(B105="","",IFERROR(VLOOKUP(B105&amp;"_"&amp;C105,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B105="","",IFERROR(VLOOKUP(E105,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G105" s="13" t="n"/>
       <c r="H105" s="16">
         <f>IF(B105="","",IFERROR(VLOOKUP(B105,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -11205,7 +10225,7 @@
       </c>
       <c r="O105" s="20" t="n"/>
       <c r="P105" s="16">
-        <f>IF(B105="","",IFERROR(N105+VLOOKUP(E105,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B105="","",IFERROR(N105+VLOOKUP(E105,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q105" s="20" t="n"/>
@@ -11244,18 +10264,15 @@
       <c r="B106" s="13" t="n"/>
       <c r="C106" s="14" t="n"/>
       <c r="D106" s="15">
-        <f>IF(B106="","",IFERROR(VLOOKUP(C106,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B106="","",IFERROR(VLOOKUP(C106,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E106" s="14" t="n"/>
       <c r="F106" s="15">
-        <f>IF(B106="","",IFERROR(VLOOKUP(E106,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G106" s="15">
-        <f>IF(B106="","",IFERROR(VLOOKUP(B106&amp;"_"&amp;C106,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B106="","",IFERROR(VLOOKUP(E106,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G106" s="13" t="n"/>
       <c r="H106" s="16">
         <f>IF(B106="","",IFERROR(VLOOKUP(B106,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -11277,7 +10294,7 @@
       </c>
       <c r="O106" s="20" t="n"/>
       <c r="P106" s="16">
-        <f>IF(B106="","",IFERROR(N106+VLOOKUP(E106,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B106="","",IFERROR(N106+VLOOKUP(E106,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q106" s="20" t="n"/>
@@ -11316,18 +10333,15 @@
       <c r="B107" s="13" t="n"/>
       <c r="C107" s="14" t="n"/>
       <c r="D107" s="15">
-        <f>IF(B107="","",IFERROR(VLOOKUP(C107,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B107="","",IFERROR(VLOOKUP(C107,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E107" s="14" t="n"/>
       <c r="F107" s="15">
-        <f>IF(B107="","",IFERROR(VLOOKUP(E107,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G107" s="15">
-        <f>IF(B107="","",IFERROR(VLOOKUP(B107&amp;"_"&amp;C107,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B107="","",IFERROR(VLOOKUP(E107,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G107" s="13" t="n"/>
       <c r="H107" s="16">
         <f>IF(B107="","",IFERROR(VLOOKUP(B107,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -11349,7 +10363,7 @@
       </c>
       <c r="O107" s="20" t="n"/>
       <c r="P107" s="16">
-        <f>IF(B107="","",IFERROR(N107+VLOOKUP(E107,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B107="","",IFERROR(N107+VLOOKUP(E107,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q107" s="20" t="n"/>
@@ -11388,18 +10402,15 @@
       <c r="B108" s="13" t="n"/>
       <c r="C108" s="14" t="n"/>
       <c r="D108" s="15">
-        <f>IF(B108="","",IFERROR(VLOOKUP(C108,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B108="","",IFERROR(VLOOKUP(C108,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E108" s="14" t="n"/>
       <c r="F108" s="15">
-        <f>IF(B108="","",IFERROR(VLOOKUP(E108,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G108" s="15">
-        <f>IF(B108="","",IFERROR(VLOOKUP(B108&amp;"_"&amp;C108,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B108="","",IFERROR(VLOOKUP(E108,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G108" s="13" t="n"/>
       <c r="H108" s="16">
         <f>IF(B108="","",IFERROR(VLOOKUP(B108,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -11421,7 +10432,7 @@
       </c>
       <c r="O108" s="20" t="n"/>
       <c r="P108" s="16">
-        <f>IF(B108="","",IFERROR(N108+VLOOKUP(E108,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B108="","",IFERROR(N108+VLOOKUP(E108,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q108" s="20" t="n"/>
@@ -11460,18 +10471,15 @@
       <c r="B109" s="13" t="n"/>
       <c r="C109" s="14" t="n"/>
       <c r="D109" s="15">
-        <f>IF(B109="","",IFERROR(VLOOKUP(C109,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B109="","",IFERROR(VLOOKUP(C109,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E109" s="14" t="n"/>
       <c r="F109" s="15">
-        <f>IF(B109="","",IFERROR(VLOOKUP(E109,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G109" s="15">
-        <f>IF(B109="","",IFERROR(VLOOKUP(B109&amp;"_"&amp;C109,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B109="","",IFERROR(VLOOKUP(E109,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G109" s="13" t="n"/>
       <c r="H109" s="16">
         <f>IF(B109="","",IFERROR(VLOOKUP(B109,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -11493,7 +10501,7 @@
       </c>
       <c r="O109" s="20" t="n"/>
       <c r="P109" s="16">
-        <f>IF(B109="","",IFERROR(N109+VLOOKUP(E109,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B109="","",IFERROR(N109+VLOOKUP(E109,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q109" s="20" t="n"/>
@@ -11532,18 +10540,15 @@
       <c r="B110" s="13" t="n"/>
       <c r="C110" s="14" t="n"/>
       <c r="D110" s="15">
-        <f>IF(B110="","",IFERROR(VLOOKUP(C110,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B110="","",IFERROR(VLOOKUP(C110,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E110" s="14" t="n"/>
       <c r="F110" s="15">
-        <f>IF(B110="","",IFERROR(VLOOKUP(E110,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G110" s="15">
-        <f>IF(B110="","",IFERROR(VLOOKUP(B110&amp;"_"&amp;C110,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B110="","",IFERROR(VLOOKUP(E110,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G110" s="13" t="n"/>
       <c r="H110" s="16">
         <f>IF(B110="","",IFERROR(VLOOKUP(B110,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -11565,7 +10570,7 @@
       </c>
       <c r="O110" s="20" t="n"/>
       <c r="P110" s="16">
-        <f>IF(B110="","",IFERROR(N110+VLOOKUP(E110,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B110="","",IFERROR(N110+VLOOKUP(E110,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q110" s="20" t="n"/>
@@ -11604,18 +10609,15 @@
       <c r="B111" s="13" t="n"/>
       <c r="C111" s="14" t="n"/>
       <c r="D111" s="15">
-        <f>IF(B111="","",IFERROR(VLOOKUP(C111,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B111="","",IFERROR(VLOOKUP(C111,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E111" s="14" t="n"/>
       <c r="F111" s="15">
-        <f>IF(B111="","",IFERROR(VLOOKUP(E111,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G111" s="15">
-        <f>IF(B111="","",IFERROR(VLOOKUP(B111&amp;"_"&amp;C111,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B111="","",IFERROR(VLOOKUP(E111,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G111" s="13" t="n"/>
       <c r="H111" s="16">
         <f>IF(B111="","",IFERROR(VLOOKUP(B111,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -11637,7 +10639,7 @@
       </c>
       <c r="O111" s="20" t="n"/>
       <c r="P111" s="16">
-        <f>IF(B111="","",IFERROR(N111+VLOOKUP(E111,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B111="","",IFERROR(N111+VLOOKUP(E111,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q111" s="20" t="n"/>
@@ -11676,18 +10678,15 @@
       <c r="B112" s="13" t="n"/>
       <c r="C112" s="14" t="n"/>
       <c r="D112" s="15">
-        <f>IF(B112="","",IFERROR(VLOOKUP(C112,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B112="","",IFERROR(VLOOKUP(C112,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E112" s="14" t="n"/>
       <c r="F112" s="15">
-        <f>IF(B112="","",IFERROR(VLOOKUP(E112,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G112" s="15">
-        <f>IF(B112="","",IFERROR(VLOOKUP(B112&amp;"_"&amp;C112,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B112="","",IFERROR(VLOOKUP(E112,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G112" s="13" t="n"/>
       <c r="H112" s="16">
         <f>IF(B112="","",IFERROR(VLOOKUP(B112,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -11709,7 +10708,7 @@
       </c>
       <c r="O112" s="20" t="n"/>
       <c r="P112" s="16">
-        <f>IF(B112="","",IFERROR(N112+VLOOKUP(E112,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B112="","",IFERROR(N112+VLOOKUP(E112,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q112" s="20" t="n"/>
@@ -11748,18 +10747,15 @@
       <c r="B113" s="13" t="n"/>
       <c r="C113" s="14" t="n"/>
       <c r="D113" s="15">
-        <f>IF(B113="","",IFERROR(VLOOKUP(C113,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B113="","",IFERROR(VLOOKUP(C113,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E113" s="14" t="n"/>
       <c r="F113" s="15">
-        <f>IF(B113="","",IFERROR(VLOOKUP(E113,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G113" s="15">
-        <f>IF(B113="","",IFERROR(VLOOKUP(B113&amp;"_"&amp;C113,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B113="","",IFERROR(VLOOKUP(E113,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G113" s="13" t="n"/>
       <c r="H113" s="16">
         <f>IF(B113="","",IFERROR(VLOOKUP(B113,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -11781,7 +10777,7 @@
       </c>
       <c r="O113" s="20" t="n"/>
       <c r="P113" s="16">
-        <f>IF(B113="","",IFERROR(N113+VLOOKUP(E113,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B113="","",IFERROR(N113+VLOOKUP(E113,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q113" s="20" t="n"/>
@@ -11820,18 +10816,15 @@
       <c r="B114" s="13" t="n"/>
       <c r="C114" s="14" t="n"/>
       <c r="D114" s="15">
-        <f>IF(B114="","",IFERROR(VLOOKUP(C114,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B114="","",IFERROR(VLOOKUP(C114,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E114" s="14" t="n"/>
       <c r="F114" s="15">
-        <f>IF(B114="","",IFERROR(VLOOKUP(E114,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G114" s="15">
-        <f>IF(B114="","",IFERROR(VLOOKUP(B114&amp;"_"&amp;C114,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B114="","",IFERROR(VLOOKUP(E114,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G114" s="13" t="n"/>
       <c r="H114" s="16">
         <f>IF(B114="","",IFERROR(VLOOKUP(B114,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -11853,7 +10846,7 @@
       </c>
       <c r="O114" s="20" t="n"/>
       <c r="P114" s="16">
-        <f>IF(B114="","",IFERROR(N114+VLOOKUP(E114,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B114="","",IFERROR(N114+VLOOKUP(E114,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q114" s="20" t="n"/>
@@ -11892,18 +10885,15 @@
       <c r="B115" s="13" t="n"/>
       <c r="C115" s="14" t="n"/>
       <c r="D115" s="15">
-        <f>IF(B115="","",IFERROR(VLOOKUP(C115,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B115="","",IFERROR(VLOOKUP(C115,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E115" s="14" t="n"/>
       <c r="F115" s="15">
-        <f>IF(B115="","",IFERROR(VLOOKUP(E115,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G115" s="15">
-        <f>IF(B115="","",IFERROR(VLOOKUP(B115&amp;"_"&amp;C115,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B115="","",IFERROR(VLOOKUP(E115,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G115" s="13" t="n"/>
       <c r="H115" s="16">
         <f>IF(B115="","",IFERROR(VLOOKUP(B115,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -11925,7 +10915,7 @@
       </c>
       <c r="O115" s="20" t="n"/>
       <c r="P115" s="16">
-        <f>IF(B115="","",IFERROR(N115+VLOOKUP(E115,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B115="","",IFERROR(N115+VLOOKUP(E115,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q115" s="20" t="n"/>
@@ -11964,18 +10954,15 @@
       <c r="B116" s="13" t="n"/>
       <c r="C116" s="14" t="n"/>
       <c r="D116" s="15">
-        <f>IF(B116="","",IFERROR(VLOOKUP(C116,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B116="","",IFERROR(VLOOKUP(C116,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E116" s="14" t="n"/>
       <c r="F116" s="15">
-        <f>IF(B116="","",IFERROR(VLOOKUP(E116,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G116" s="15">
-        <f>IF(B116="","",IFERROR(VLOOKUP(B116&amp;"_"&amp;C116,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B116="","",IFERROR(VLOOKUP(E116,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G116" s="13" t="n"/>
       <c r="H116" s="16">
         <f>IF(B116="","",IFERROR(VLOOKUP(B116,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -11997,7 +10984,7 @@
       </c>
       <c r="O116" s="20" t="n"/>
       <c r="P116" s="16">
-        <f>IF(B116="","",IFERROR(N116+VLOOKUP(E116,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B116="","",IFERROR(N116+VLOOKUP(E116,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q116" s="20" t="n"/>
@@ -12036,18 +11023,15 @@
       <c r="B117" s="13" t="n"/>
       <c r="C117" s="14" t="n"/>
       <c r="D117" s="15">
-        <f>IF(B117="","",IFERROR(VLOOKUP(C117,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B117="","",IFERROR(VLOOKUP(C117,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E117" s="14" t="n"/>
       <c r="F117" s="15">
-        <f>IF(B117="","",IFERROR(VLOOKUP(E117,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G117" s="15">
-        <f>IF(B117="","",IFERROR(VLOOKUP(B117&amp;"_"&amp;C117,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B117="","",IFERROR(VLOOKUP(E117,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G117" s="13" t="n"/>
       <c r="H117" s="16">
         <f>IF(B117="","",IFERROR(VLOOKUP(B117,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -12069,7 +11053,7 @@
       </c>
       <c r="O117" s="20" t="n"/>
       <c r="P117" s="16">
-        <f>IF(B117="","",IFERROR(N117+VLOOKUP(E117,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B117="","",IFERROR(N117+VLOOKUP(E117,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q117" s="20" t="n"/>
@@ -12108,18 +11092,15 @@
       <c r="B118" s="13" t="n"/>
       <c r="C118" s="14" t="n"/>
       <c r="D118" s="15">
-        <f>IF(B118="","",IFERROR(VLOOKUP(C118,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B118="","",IFERROR(VLOOKUP(C118,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E118" s="14" t="n"/>
       <c r="F118" s="15">
-        <f>IF(B118="","",IFERROR(VLOOKUP(E118,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G118" s="15">
-        <f>IF(B118="","",IFERROR(VLOOKUP(B118&amp;"_"&amp;C118,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B118="","",IFERROR(VLOOKUP(E118,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G118" s="13" t="n"/>
       <c r="H118" s="16">
         <f>IF(B118="","",IFERROR(VLOOKUP(B118,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -12141,7 +11122,7 @@
       </c>
       <c r="O118" s="20" t="n"/>
       <c r="P118" s="16">
-        <f>IF(B118="","",IFERROR(N118+VLOOKUP(E118,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B118="","",IFERROR(N118+VLOOKUP(E118,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q118" s="20" t="n"/>
@@ -12180,18 +11161,15 @@
       <c r="B119" s="13" t="n"/>
       <c r="C119" s="14" t="n"/>
       <c r="D119" s="15">
-        <f>IF(B119="","",IFERROR(VLOOKUP(C119,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B119="","",IFERROR(VLOOKUP(C119,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E119" s="14" t="n"/>
       <c r="F119" s="15">
-        <f>IF(B119="","",IFERROR(VLOOKUP(E119,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G119" s="15">
-        <f>IF(B119="","",IFERROR(VLOOKUP(B119&amp;"_"&amp;C119,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B119="","",IFERROR(VLOOKUP(E119,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G119" s="13" t="n"/>
       <c r="H119" s="16">
         <f>IF(B119="","",IFERROR(VLOOKUP(B119,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -12213,7 +11191,7 @@
       </c>
       <c r="O119" s="20" t="n"/>
       <c r="P119" s="16">
-        <f>IF(B119="","",IFERROR(N119+VLOOKUP(E119,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B119="","",IFERROR(N119+VLOOKUP(E119,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q119" s="20" t="n"/>
@@ -12252,18 +11230,15 @@
       <c r="B120" s="13" t="n"/>
       <c r="C120" s="14" t="n"/>
       <c r="D120" s="15">
-        <f>IF(B120="","",IFERROR(VLOOKUP(C120,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B120="","",IFERROR(VLOOKUP(C120,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E120" s="14" t="n"/>
       <c r="F120" s="15">
-        <f>IF(B120="","",IFERROR(VLOOKUP(E120,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G120" s="15">
-        <f>IF(B120="","",IFERROR(VLOOKUP(B120&amp;"_"&amp;C120,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B120="","",IFERROR(VLOOKUP(E120,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G120" s="13" t="n"/>
       <c r="H120" s="16">
         <f>IF(B120="","",IFERROR(VLOOKUP(B120,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -12285,7 +11260,7 @@
       </c>
       <c r="O120" s="20" t="n"/>
       <c r="P120" s="16">
-        <f>IF(B120="","",IFERROR(N120+VLOOKUP(E120,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B120="","",IFERROR(N120+VLOOKUP(E120,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q120" s="20" t="n"/>
@@ -12324,18 +11299,15 @@
       <c r="B121" s="13" t="n"/>
       <c r="C121" s="14" t="n"/>
       <c r="D121" s="15">
-        <f>IF(B121="","",IFERROR(VLOOKUP(C121,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B121="","",IFERROR(VLOOKUP(C121,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E121" s="14" t="n"/>
       <c r="F121" s="15">
-        <f>IF(B121="","",IFERROR(VLOOKUP(E121,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G121" s="15">
-        <f>IF(B121="","",IFERROR(VLOOKUP(B121&amp;"_"&amp;C121,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B121="","",IFERROR(VLOOKUP(E121,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G121" s="13" t="n"/>
       <c r="H121" s="16">
         <f>IF(B121="","",IFERROR(VLOOKUP(B121,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -12357,7 +11329,7 @@
       </c>
       <c r="O121" s="20" t="n"/>
       <c r="P121" s="16">
-        <f>IF(B121="","",IFERROR(N121+VLOOKUP(E121,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B121="","",IFERROR(N121+VLOOKUP(E121,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q121" s="20" t="n"/>
@@ -12396,18 +11368,15 @@
       <c r="B122" s="13" t="n"/>
       <c r="C122" s="14" t="n"/>
       <c r="D122" s="15">
-        <f>IF(B122="","",IFERROR(VLOOKUP(C122,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B122="","",IFERROR(VLOOKUP(C122,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E122" s="14" t="n"/>
       <c r="F122" s="15">
-        <f>IF(B122="","",IFERROR(VLOOKUP(E122,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G122" s="15">
-        <f>IF(B122="","",IFERROR(VLOOKUP(B122&amp;"_"&amp;C122,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B122="","",IFERROR(VLOOKUP(E122,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G122" s="13" t="n"/>
       <c r="H122" s="16">
         <f>IF(B122="","",IFERROR(VLOOKUP(B122,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -12429,7 +11398,7 @@
       </c>
       <c r="O122" s="20" t="n"/>
       <c r="P122" s="16">
-        <f>IF(B122="","",IFERROR(N122+VLOOKUP(E122,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B122="","",IFERROR(N122+VLOOKUP(E122,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q122" s="20" t="n"/>
@@ -12468,18 +11437,15 @@
       <c r="B123" s="13" t="n"/>
       <c r="C123" s="14" t="n"/>
       <c r="D123" s="15">
-        <f>IF(B123="","",IFERROR(VLOOKUP(C123,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B123="","",IFERROR(VLOOKUP(C123,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E123" s="14" t="n"/>
       <c r="F123" s="15">
-        <f>IF(B123="","",IFERROR(VLOOKUP(E123,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G123" s="15">
-        <f>IF(B123="","",IFERROR(VLOOKUP(B123&amp;"_"&amp;C123,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B123="","",IFERROR(VLOOKUP(E123,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G123" s="13" t="n"/>
       <c r="H123" s="16">
         <f>IF(B123="","",IFERROR(VLOOKUP(B123,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -12501,7 +11467,7 @@
       </c>
       <c r="O123" s="20" t="n"/>
       <c r="P123" s="16">
-        <f>IF(B123="","",IFERROR(N123+VLOOKUP(E123,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B123="","",IFERROR(N123+VLOOKUP(E123,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q123" s="20" t="n"/>
@@ -12540,18 +11506,15 @@
       <c r="B124" s="13" t="n"/>
       <c r="C124" s="14" t="n"/>
       <c r="D124" s="15">
-        <f>IF(B124="","",IFERROR(VLOOKUP(C124,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B124="","",IFERROR(VLOOKUP(C124,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E124" s="14" t="n"/>
       <c r="F124" s="15">
-        <f>IF(B124="","",IFERROR(VLOOKUP(E124,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G124" s="15">
-        <f>IF(B124="","",IFERROR(VLOOKUP(B124&amp;"_"&amp;C124,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B124="","",IFERROR(VLOOKUP(E124,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G124" s="13" t="n"/>
       <c r="H124" s="16">
         <f>IF(B124="","",IFERROR(VLOOKUP(B124,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -12573,7 +11536,7 @@
       </c>
       <c r="O124" s="20" t="n"/>
       <c r="P124" s="16">
-        <f>IF(B124="","",IFERROR(N124+VLOOKUP(E124,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B124="","",IFERROR(N124+VLOOKUP(E124,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q124" s="20" t="n"/>
@@ -12612,18 +11575,15 @@
       <c r="B125" s="13" t="n"/>
       <c r="C125" s="14" t="n"/>
       <c r="D125" s="15">
-        <f>IF(B125="","",IFERROR(VLOOKUP(C125,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B125="","",IFERROR(VLOOKUP(C125,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E125" s="14" t="n"/>
       <c r="F125" s="15">
-        <f>IF(B125="","",IFERROR(VLOOKUP(E125,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G125" s="15">
-        <f>IF(B125="","",IFERROR(VLOOKUP(B125&amp;"_"&amp;C125,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B125="","",IFERROR(VLOOKUP(E125,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G125" s="13" t="n"/>
       <c r="H125" s="16">
         <f>IF(B125="","",IFERROR(VLOOKUP(B125,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -12645,7 +11605,7 @@
       </c>
       <c r="O125" s="20" t="n"/>
       <c r="P125" s="16">
-        <f>IF(B125="","",IFERROR(N125+VLOOKUP(E125,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B125="","",IFERROR(N125+VLOOKUP(E125,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q125" s="20" t="n"/>
@@ -12684,18 +11644,15 @@
       <c r="B126" s="13" t="n"/>
       <c r="C126" s="14" t="n"/>
       <c r="D126" s="15">
-        <f>IF(B126="","",IFERROR(VLOOKUP(C126,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B126="","",IFERROR(VLOOKUP(C126,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E126" s="14" t="n"/>
       <c r="F126" s="15">
-        <f>IF(B126="","",IFERROR(VLOOKUP(E126,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G126" s="15">
-        <f>IF(B126="","",IFERROR(VLOOKUP(B126&amp;"_"&amp;C126,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B126="","",IFERROR(VLOOKUP(E126,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G126" s="13" t="n"/>
       <c r="H126" s="16">
         <f>IF(B126="","",IFERROR(VLOOKUP(B126,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -12717,7 +11674,7 @@
       </c>
       <c r="O126" s="20" t="n"/>
       <c r="P126" s="16">
-        <f>IF(B126="","",IFERROR(N126+VLOOKUP(E126,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B126="","",IFERROR(N126+VLOOKUP(E126,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q126" s="20" t="n"/>
@@ -12756,18 +11713,15 @@
       <c r="B127" s="13" t="n"/>
       <c r="C127" s="14" t="n"/>
       <c r="D127" s="15">
-        <f>IF(B127="","",IFERROR(VLOOKUP(C127,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B127="","",IFERROR(VLOOKUP(C127,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E127" s="14" t="n"/>
       <c r="F127" s="15">
-        <f>IF(B127="","",IFERROR(VLOOKUP(E127,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G127" s="15">
-        <f>IF(B127="","",IFERROR(VLOOKUP(B127&amp;"_"&amp;C127,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B127="","",IFERROR(VLOOKUP(E127,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G127" s="13" t="n"/>
       <c r="H127" s="16">
         <f>IF(B127="","",IFERROR(VLOOKUP(B127,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -12789,7 +11743,7 @@
       </c>
       <c r="O127" s="20" t="n"/>
       <c r="P127" s="16">
-        <f>IF(B127="","",IFERROR(N127+VLOOKUP(E127,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B127="","",IFERROR(N127+VLOOKUP(E127,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q127" s="20" t="n"/>
@@ -12828,18 +11782,15 @@
       <c r="B128" s="13" t="n"/>
       <c r="C128" s="14" t="n"/>
       <c r="D128" s="15">
-        <f>IF(B128="","",IFERROR(VLOOKUP(C128,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B128="","",IFERROR(VLOOKUP(C128,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E128" s="14" t="n"/>
       <c r="F128" s="15">
-        <f>IF(B128="","",IFERROR(VLOOKUP(E128,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G128" s="15">
-        <f>IF(B128="","",IFERROR(VLOOKUP(B128&amp;"_"&amp;C128,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B128="","",IFERROR(VLOOKUP(E128,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G128" s="13" t="n"/>
       <c r="H128" s="16">
         <f>IF(B128="","",IFERROR(VLOOKUP(B128,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -12861,7 +11812,7 @@
       </c>
       <c r="O128" s="20" t="n"/>
       <c r="P128" s="16">
-        <f>IF(B128="","",IFERROR(N128+VLOOKUP(E128,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B128="","",IFERROR(N128+VLOOKUP(E128,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q128" s="20" t="n"/>
@@ -12900,18 +11851,15 @@
       <c r="B129" s="13" t="n"/>
       <c r="C129" s="14" t="n"/>
       <c r="D129" s="15">
-        <f>IF(B129="","",IFERROR(VLOOKUP(C129,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B129="","",IFERROR(VLOOKUP(C129,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E129" s="14" t="n"/>
       <c r="F129" s="15">
-        <f>IF(B129="","",IFERROR(VLOOKUP(E129,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G129" s="15">
-        <f>IF(B129="","",IFERROR(VLOOKUP(B129&amp;"_"&amp;C129,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B129="","",IFERROR(VLOOKUP(E129,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G129" s="13" t="n"/>
       <c r="H129" s="16">
         <f>IF(B129="","",IFERROR(VLOOKUP(B129,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -12933,7 +11881,7 @@
       </c>
       <c r="O129" s="20" t="n"/>
       <c r="P129" s="16">
-        <f>IF(B129="","",IFERROR(N129+VLOOKUP(E129,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B129="","",IFERROR(N129+VLOOKUP(E129,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q129" s="20" t="n"/>
@@ -12972,18 +11920,15 @@
       <c r="B130" s="13" t="n"/>
       <c r="C130" s="14" t="n"/>
       <c r="D130" s="15">
-        <f>IF(B130="","",IFERROR(VLOOKUP(C130,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B130="","",IFERROR(VLOOKUP(C130,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E130" s="14" t="n"/>
       <c r="F130" s="15">
-        <f>IF(B130="","",IFERROR(VLOOKUP(E130,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G130" s="15">
-        <f>IF(B130="","",IFERROR(VLOOKUP(B130&amp;"_"&amp;C130,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B130="","",IFERROR(VLOOKUP(E130,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G130" s="13" t="n"/>
       <c r="H130" s="16">
         <f>IF(B130="","",IFERROR(VLOOKUP(B130,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -13005,7 +11950,7 @@
       </c>
       <c r="O130" s="20" t="n"/>
       <c r="P130" s="16">
-        <f>IF(B130="","",IFERROR(N130+VLOOKUP(E130,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B130="","",IFERROR(N130+VLOOKUP(E130,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q130" s="20" t="n"/>
@@ -13044,18 +11989,15 @@
       <c r="B131" s="13" t="n"/>
       <c r="C131" s="14" t="n"/>
       <c r="D131" s="15">
-        <f>IF(B131="","",IFERROR(VLOOKUP(C131,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B131="","",IFERROR(VLOOKUP(C131,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E131" s="14" t="n"/>
       <c r="F131" s="15">
-        <f>IF(B131="","",IFERROR(VLOOKUP(E131,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G131" s="15">
-        <f>IF(B131="","",IFERROR(VLOOKUP(B131&amp;"_"&amp;C131,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B131="","",IFERROR(VLOOKUP(E131,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G131" s="13" t="n"/>
       <c r="H131" s="16">
         <f>IF(B131="","",IFERROR(VLOOKUP(B131,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -13077,7 +12019,7 @@
       </c>
       <c r="O131" s="20" t="n"/>
       <c r="P131" s="16">
-        <f>IF(B131="","",IFERROR(N131+VLOOKUP(E131,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B131="","",IFERROR(N131+VLOOKUP(E131,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q131" s="20" t="n"/>
@@ -13116,18 +12058,15 @@
       <c r="B132" s="13" t="n"/>
       <c r="C132" s="14" t="n"/>
       <c r="D132" s="15">
-        <f>IF(B132="","",IFERROR(VLOOKUP(C132,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B132="","",IFERROR(VLOOKUP(C132,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E132" s="14" t="n"/>
       <c r="F132" s="15">
-        <f>IF(B132="","",IFERROR(VLOOKUP(E132,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G132" s="15">
-        <f>IF(B132="","",IFERROR(VLOOKUP(B132&amp;"_"&amp;C132,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B132="","",IFERROR(VLOOKUP(E132,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G132" s="13" t="n"/>
       <c r="H132" s="16">
         <f>IF(B132="","",IFERROR(VLOOKUP(B132,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -13149,7 +12088,7 @@
       </c>
       <c r="O132" s="20" t="n"/>
       <c r="P132" s="16">
-        <f>IF(B132="","",IFERROR(N132+VLOOKUP(E132,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B132="","",IFERROR(N132+VLOOKUP(E132,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q132" s="20" t="n"/>
@@ -13188,18 +12127,15 @@
       <c r="B133" s="13" t="n"/>
       <c r="C133" s="14" t="n"/>
       <c r="D133" s="15">
-        <f>IF(B133="","",IFERROR(VLOOKUP(C133,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B133="","",IFERROR(VLOOKUP(C133,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E133" s="14" t="n"/>
       <c r="F133" s="15">
-        <f>IF(B133="","",IFERROR(VLOOKUP(E133,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G133" s="15">
-        <f>IF(B133="","",IFERROR(VLOOKUP(B133&amp;"_"&amp;C133,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B133="","",IFERROR(VLOOKUP(E133,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G133" s="13" t="n"/>
       <c r="H133" s="16">
         <f>IF(B133="","",IFERROR(VLOOKUP(B133,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -13221,7 +12157,7 @@
       </c>
       <c r="O133" s="20" t="n"/>
       <c r="P133" s="16">
-        <f>IF(B133="","",IFERROR(N133+VLOOKUP(E133,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B133="","",IFERROR(N133+VLOOKUP(E133,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q133" s="20" t="n"/>
@@ -13260,18 +12196,15 @@
       <c r="B134" s="13" t="n"/>
       <c r="C134" s="14" t="n"/>
       <c r="D134" s="15">
-        <f>IF(B134="","",IFERROR(VLOOKUP(C134,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B134="","",IFERROR(VLOOKUP(C134,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E134" s="14" t="n"/>
       <c r="F134" s="15">
-        <f>IF(B134="","",IFERROR(VLOOKUP(E134,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G134" s="15">
-        <f>IF(B134="","",IFERROR(VLOOKUP(B134&amp;"_"&amp;C134,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B134="","",IFERROR(VLOOKUP(E134,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G134" s="13" t="n"/>
       <c r="H134" s="16">
         <f>IF(B134="","",IFERROR(VLOOKUP(B134,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -13293,7 +12226,7 @@
       </c>
       <c r="O134" s="20" t="n"/>
       <c r="P134" s="16">
-        <f>IF(B134="","",IFERROR(N134+VLOOKUP(E134,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B134="","",IFERROR(N134+VLOOKUP(E134,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q134" s="20" t="n"/>
@@ -13332,18 +12265,15 @@
       <c r="B135" s="13" t="n"/>
       <c r="C135" s="14" t="n"/>
       <c r="D135" s="15">
-        <f>IF(B135="","",IFERROR(VLOOKUP(C135,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B135="","",IFERROR(VLOOKUP(C135,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E135" s="14" t="n"/>
       <c r="F135" s="15">
-        <f>IF(B135="","",IFERROR(VLOOKUP(E135,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G135" s="15">
-        <f>IF(B135="","",IFERROR(VLOOKUP(B135&amp;"_"&amp;C135,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B135="","",IFERROR(VLOOKUP(E135,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G135" s="13" t="n"/>
       <c r="H135" s="16">
         <f>IF(B135="","",IFERROR(VLOOKUP(B135,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -13365,7 +12295,7 @@
       </c>
       <c r="O135" s="20" t="n"/>
       <c r="P135" s="16">
-        <f>IF(B135="","",IFERROR(N135+VLOOKUP(E135,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B135="","",IFERROR(N135+VLOOKUP(E135,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q135" s="20" t="n"/>
@@ -13404,18 +12334,15 @@
       <c r="B136" s="13" t="n"/>
       <c r="C136" s="14" t="n"/>
       <c r="D136" s="15">
-        <f>IF(B136="","",IFERROR(VLOOKUP(C136,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B136="","",IFERROR(VLOOKUP(C136,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E136" s="14" t="n"/>
       <c r="F136" s="15">
-        <f>IF(B136="","",IFERROR(VLOOKUP(E136,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G136" s="15">
-        <f>IF(B136="","",IFERROR(VLOOKUP(B136&amp;"_"&amp;C136,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B136="","",IFERROR(VLOOKUP(E136,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G136" s="13" t="n"/>
       <c r="H136" s="16">
         <f>IF(B136="","",IFERROR(VLOOKUP(B136,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -13437,7 +12364,7 @@
       </c>
       <c r="O136" s="20" t="n"/>
       <c r="P136" s="16">
-        <f>IF(B136="","",IFERROR(N136+VLOOKUP(E136,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B136="","",IFERROR(N136+VLOOKUP(E136,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q136" s="20" t="n"/>
@@ -13476,18 +12403,15 @@
       <c r="B137" s="13" t="n"/>
       <c r="C137" s="14" t="n"/>
       <c r="D137" s="15">
-        <f>IF(B137="","",IFERROR(VLOOKUP(C137,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B137="","",IFERROR(VLOOKUP(C137,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E137" s="14" t="n"/>
       <c r="F137" s="15">
-        <f>IF(B137="","",IFERROR(VLOOKUP(E137,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G137" s="15">
-        <f>IF(B137="","",IFERROR(VLOOKUP(B137&amp;"_"&amp;C137,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B137="","",IFERROR(VLOOKUP(E137,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G137" s="13" t="n"/>
       <c r="H137" s="16">
         <f>IF(B137="","",IFERROR(VLOOKUP(B137,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -13509,7 +12433,7 @@
       </c>
       <c r="O137" s="20" t="n"/>
       <c r="P137" s="16">
-        <f>IF(B137="","",IFERROR(N137+VLOOKUP(E137,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B137="","",IFERROR(N137+VLOOKUP(E137,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q137" s="20" t="n"/>
@@ -13548,18 +12472,15 @@
       <c r="B138" s="13" t="n"/>
       <c r="C138" s="14" t="n"/>
       <c r="D138" s="15">
-        <f>IF(B138="","",IFERROR(VLOOKUP(C138,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B138="","",IFERROR(VLOOKUP(C138,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E138" s="14" t="n"/>
       <c r="F138" s="15">
-        <f>IF(B138="","",IFERROR(VLOOKUP(E138,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G138" s="15">
-        <f>IF(B138="","",IFERROR(VLOOKUP(B138&amp;"_"&amp;C138,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B138="","",IFERROR(VLOOKUP(E138,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G138" s="13" t="n"/>
       <c r="H138" s="16">
         <f>IF(B138="","",IFERROR(VLOOKUP(B138,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -13581,7 +12502,7 @@
       </c>
       <c r="O138" s="20" t="n"/>
       <c r="P138" s="16">
-        <f>IF(B138="","",IFERROR(N138+VLOOKUP(E138,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B138="","",IFERROR(N138+VLOOKUP(E138,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q138" s="20" t="n"/>
@@ -13620,18 +12541,15 @@
       <c r="B139" s="13" t="n"/>
       <c r="C139" s="14" t="n"/>
       <c r="D139" s="15">
-        <f>IF(B139="","",IFERROR(VLOOKUP(C139,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B139="","",IFERROR(VLOOKUP(C139,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E139" s="14" t="n"/>
       <c r="F139" s="15">
-        <f>IF(B139="","",IFERROR(VLOOKUP(E139,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G139" s="15">
-        <f>IF(B139="","",IFERROR(VLOOKUP(B139&amp;"_"&amp;C139,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B139="","",IFERROR(VLOOKUP(E139,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G139" s="13" t="n"/>
       <c r="H139" s="16">
         <f>IF(B139="","",IFERROR(VLOOKUP(B139,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -13653,7 +12571,7 @@
       </c>
       <c r="O139" s="20" t="n"/>
       <c r="P139" s="16">
-        <f>IF(B139="","",IFERROR(N139+VLOOKUP(E139,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B139="","",IFERROR(N139+VLOOKUP(E139,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q139" s="20" t="n"/>
@@ -13692,18 +12610,15 @@
       <c r="B140" s="13" t="n"/>
       <c r="C140" s="14" t="n"/>
       <c r="D140" s="15">
-        <f>IF(B140="","",IFERROR(VLOOKUP(C140,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B140="","",IFERROR(VLOOKUP(C140,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E140" s="14" t="n"/>
       <c r="F140" s="15">
-        <f>IF(B140="","",IFERROR(VLOOKUP(E140,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G140" s="15">
-        <f>IF(B140="","",IFERROR(VLOOKUP(B140&amp;"_"&amp;C140,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B140="","",IFERROR(VLOOKUP(E140,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G140" s="13" t="n"/>
       <c r="H140" s="16">
         <f>IF(B140="","",IFERROR(VLOOKUP(B140,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -13725,7 +12640,7 @@
       </c>
       <c r="O140" s="20" t="n"/>
       <c r="P140" s="16">
-        <f>IF(B140="","",IFERROR(N140+VLOOKUP(E140,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B140="","",IFERROR(N140+VLOOKUP(E140,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q140" s="20" t="n"/>
@@ -13764,18 +12679,15 @@
       <c r="B141" s="13" t="n"/>
       <c r="C141" s="14" t="n"/>
       <c r="D141" s="15">
-        <f>IF(B141="","",IFERROR(VLOOKUP(C141,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B141="","",IFERROR(VLOOKUP(C141,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E141" s="14" t="n"/>
       <c r="F141" s="15">
-        <f>IF(B141="","",IFERROR(VLOOKUP(E141,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G141" s="15">
-        <f>IF(B141="","",IFERROR(VLOOKUP(B141&amp;"_"&amp;C141,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B141="","",IFERROR(VLOOKUP(E141,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G141" s="13" t="n"/>
       <c r="H141" s="16">
         <f>IF(B141="","",IFERROR(VLOOKUP(B141,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -13797,7 +12709,7 @@
       </c>
       <c r="O141" s="20" t="n"/>
       <c r="P141" s="16">
-        <f>IF(B141="","",IFERROR(N141+VLOOKUP(E141,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B141="","",IFERROR(N141+VLOOKUP(E141,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q141" s="20" t="n"/>
@@ -13836,18 +12748,15 @@
       <c r="B142" s="13" t="n"/>
       <c r="C142" s="14" t="n"/>
       <c r="D142" s="15">
-        <f>IF(B142="","",IFERROR(VLOOKUP(C142,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B142="","",IFERROR(VLOOKUP(C142,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E142" s="14" t="n"/>
       <c r="F142" s="15">
-        <f>IF(B142="","",IFERROR(VLOOKUP(E142,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G142" s="15">
-        <f>IF(B142="","",IFERROR(VLOOKUP(B142&amp;"_"&amp;C142,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B142="","",IFERROR(VLOOKUP(E142,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G142" s="13" t="n"/>
       <c r="H142" s="16">
         <f>IF(B142="","",IFERROR(VLOOKUP(B142,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -13869,7 +12778,7 @@
       </c>
       <c r="O142" s="20" t="n"/>
       <c r="P142" s="16">
-        <f>IF(B142="","",IFERROR(N142+VLOOKUP(E142,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B142="","",IFERROR(N142+VLOOKUP(E142,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q142" s="20" t="n"/>
@@ -13908,18 +12817,15 @@
       <c r="B143" s="13" t="n"/>
       <c r="C143" s="14" t="n"/>
       <c r="D143" s="15">
-        <f>IF(B143="","",IFERROR(VLOOKUP(C143,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B143="","",IFERROR(VLOOKUP(C143,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E143" s="14" t="n"/>
       <c r="F143" s="15">
-        <f>IF(B143="","",IFERROR(VLOOKUP(E143,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G143" s="15">
-        <f>IF(B143="","",IFERROR(VLOOKUP(B143&amp;"_"&amp;C143,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B143="","",IFERROR(VLOOKUP(E143,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G143" s="13" t="n"/>
       <c r="H143" s="16">
         <f>IF(B143="","",IFERROR(VLOOKUP(B143,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -13941,7 +12847,7 @@
       </c>
       <c r="O143" s="20" t="n"/>
       <c r="P143" s="16">
-        <f>IF(B143="","",IFERROR(N143+VLOOKUP(E143,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B143="","",IFERROR(N143+VLOOKUP(E143,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q143" s="20" t="n"/>
@@ -13980,18 +12886,15 @@
       <c r="B144" s="13" t="n"/>
       <c r="C144" s="14" t="n"/>
       <c r="D144" s="15">
-        <f>IF(B144="","",IFERROR(VLOOKUP(C144,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B144="","",IFERROR(VLOOKUP(C144,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E144" s="14" t="n"/>
       <c r="F144" s="15">
-        <f>IF(B144="","",IFERROR(VLOOKUP(E144,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G144" s="15">
-        <f>IF(B144="","",IFERROR(VLOOKUP(B144&amp;"_"&amp;C144,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B144="","",IFERROR(VLOOKUP(E144,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G144" s="13" t="n"/>
       <c r="H144" s="16">
         <f>IF(B144="","",IFERROR(VLOOKUP(B144,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -14013,7 +12916,7 @@
       </c>
       <c r="O144" s="20" t="n"/>
       <c r="P144" s="16">
-        <f>IF(B144="","",IFERROR(N144+VLOOKUP(E144,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B144="","",IFERROR(N144+VLOOKUP(E144,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q144" s="20" t="n"/>
@@ -14052,18 +12955,15 @@
       <c r="B145" s="13" t="n"/>
       <c r="C145" s="14" t="n"/>
       <c r="D145" s="15">
-        <f>IF(B145="","",IFERROR(VLOOKUP(C145,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B145="","",IFERROR(VLOOKUP(C145,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E145" s="14" t="n"/>
       <c r="F145" s="15">
-        <f>IF(B145="","",IFERROR(VLOOKUP(E145,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G145" s="15">
-        <f>IF(B145="","",IFERROR(VLOOKUP(B145&amp;"_"&amp;C145,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B145="","",IFERROR(VLOOKUP(E145,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G145" s="13" t="n"/>
       <c r="H145" s="16">
         <f>IF(B145="","",IFERROR(VLOOKUP(B145,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -14085,7 +12985,7 @@
       </c>
       <c r="O145" s="20" t="n"/>
       <c r="P145" s="16">
-        <f>IF(B145="","",IFERROR(N145+VLOOKUP(E145,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B145="","",IFERROR(N145+VLOOKUP(E145,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q145" s="20" t="n"/>
@@ -14124,18 +13024,15 @@
       <c r="B146" s="13" t="n"/>
       <c r="C146" s="14" t="n"/>
       <c r="D146" s="15">
-        <f>IF(B146="","",IFERROR(VLOOKUP(C146,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B146="","",IFERROR(VLOOKUP(C146,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E146" s="14" t="n"/>
       <c r="F146" s="15">
-        <f>IF(B146="","",IFERROR(VLOOKUP(E146,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G146" s="15">
-        <f>IF(B146="","",IFERROR(VLOOKUP(B146&amp;"_"&amp;C146,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B146="","",IFERROR(VLOOKUP(E146,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G146" s="13" t="n"/>
       <c r="H146" s="16">
         <f>IF(B146="","",IFERROR(VLOOKUP(B146,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -14157,7 +13054,7 @@
       </c>
       <c r="O146" s="20" t="n"/>
       <c r="P146" s="16">
-        <f>IF(B146="","",IFERROR(N146+VLOOKUP(E146,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B146="","",IFERROR(N146+VLOOKUP(E146,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q146" s="20" t="n"/>
@@ -14196,18 +13093,15 @@
       <c r="B147" s="13" t="n"/>
       <c r="C147" s="14" t="n"/>
       <c r="D147" s="15">
-        <f>IF(B147="","",IFERROR(VLOOKUP(C147,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B147="","",IFERROR(VLOOKUP(C147,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E147" s="14" t="n"/>
       <c r="F147" s="15">
-        <f>IF(B147="","",IFERROR(VLOOKUP(E147,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G147" s="15">
-        <f>IF(B147="","",IFERROR(VLOOKUP(B147&amp;"_"&amp;C147,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B147="","",IFERROR(VLOOKUP(E147,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G147" s="13" t="n"/>
       <c r="H147" s="16">
         <f>IF(B147="","",IFERROR(VLOOKUP(B147,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -14229,7 +13123,7 @@
       </c>
       <c r="O147" s="20" t="n"/>
       <c r="P147" s="16">
-        <f>IF(B147="","",IFERROR(N147+VLOOKUP(E147,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B147="","",IFERROR(N147+VLOOKUP(E147,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q147" s="20" t="n"/>
@@ -14268,18 +13162,15 @@
       <c r="B148" s="13" t="n"/>
       <c r="C148" s="14" t="n"/>
       <c r="D148" s="15">
-        <f>IF(B148="","",IFERROR(VLOOKUP(C148,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B148="","",IFERROR(VLOOKUP(C148,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E148" s="14" t="n"/>
       <c r="F148" s="15">
-        <f>IF(B148="","",IFERROR(VLOOKUP(E148,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G148" s="15">
-        <f>IF(B148="","",IFERROR(VLOOKUP(B148&amp;"_"&amp;C148,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B148="","",IFERROR(VLOOKUP(E148,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G148" s="13" t="n"/>
       <c r="H148" s="16">
         <f>IF(B148="","",IFERROR(VLOOKUP(B148,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -14301,7 +13192,7 @@
       </c>
       <c r="O148" s="20" t="n"/>
       <c r="P148" s="16">
-        <f>IF(B148="","",IFERROR(N148+VLOOKUP(E148,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B148="","",IFERROR(N148+VLOOKUP(E148,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q148" s="20" t="n"/>
@@ -14340,18 +13231,15 @@
       <c r="B149" s="13" t="n"/>
       <c r="C149" s="14" t="n"/>
       <c r="D149" s="15">
-        <f>IF(B149="","",IFERROR(VLOOKUP(C149,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B149="","",IFERROR(VLOOKUP(C149,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E149" s="14" t="n"/>
       <c r="F149" s="15">
-        <f>IF(B149="","",IFERROR(VLOOKUP(E149,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G149" s="15">
-        <f>IF(B149="","",IFERROR(VLOOKUP(B149&amp;"_"&amp;C149,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B149="","",IFERROR(VLOOKUP(E149,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G149" s="13" t="n"/>
       <c r="H149" s="16">
         <f>IF(B149="","",IFERROR(VLOOKUP(B149,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -14373,7 +13261,7 @@
       </c>
       <c r="O149" s="20" t="n"/>
       <c r="P149" s="16">
-        <f>IF(B149="","",IFERROR(N149+VLOOKUP(E149,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B149="","",IFERROR(N149+VLOOKUP(E149,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q149" s="20" t="n"/>
@@ -14412,18 +13300,15 @@
       <c r="B150" s="13" t="n"/>
       <c r="C150" s="14" t="n"/>
       <c r="D150" s="15">
-        <f>IF(B150="","",IFERROR(VLOOKUP(C150,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B150="","",IFERROR(VLOOKUP(C150,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E150" s="14" t="n"/>
       <c r="F150" s="15">
-        <f>IF(B150="","",IFERROR(VLOOKUP(E150,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G150" s="15">
-        <f>IF(B150="","",IFERROR(VLOOKUP(B150&amp;"_"&amp;C150,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B150="","",IFERROR(VLOOKUP(E150,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G150" s="13" t="n"/>
       <c r="H150" s="16">
         <f>IF(B150="","",IFERROR(VLOOKUP(B150,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -14445,7 +13330,7 @@
       </c>
       <c r="O150" s="20" t="n"/>
       <c r="P150" s="16">
-        <f>IF(B150="","",IFERROR(N150+VLOOKUP(E150,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B150="","",IFERROR(N150+VLOOKUP(E150,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q150" s="20" t="n"/>
@@ -14484,18 +13369,15 @@
       <c r="B151" s="13" t="n"/>
       <c r="C151" s="14" t="n"/>
       <c r="D151" s="15">
-        <f>IF(B151="","",IFERROR(VLOOKUP(C151,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B151="","",IFERROR(VLOOKUP(C151,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E151" s="14" t="n"/>
       <c r="F151" s="15">
-        <f>IF(B151="","",IFERROR(VLOOKUP(E151,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G151" s="15">
-        <f>IF(B151="","",IFERROR(VLOOKUP(B151&amp;"_"&amp;C151,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B151="","",IFERROR(VLOOKUP(E151,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G151" s="13" t="n"/>
       <c r="H151" s="16">
         <f>IF(B151="","",IFERROR(VLOOKUP(B151,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -14517,7 +13399,7 @@
       </c>
       <c r="O151" s="20" t="n"/>
       <c r="P151" s="16">
-        <f>IF(B151="","",IFERROR(N151+VLOOKUP(E151,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B151="","",IFERROR(N151+VLOOKUP(E151,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q151" s="20" t="n"/>
@@ -14556,18 +13438,15 @@
       <c r="B152" s="13" t="n"/>
       <c r="C152" s="14" t="n"/>
       <c r="D152" s="15">
-        <f>IF(B152="","",IFERROR(VLOOKUP(C152,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B152="","",IFERROR(VLOOKUP(C152,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E152" s="14" t="n"/>
       <c r="F152" s="15">
-        <f>IF(B152="","",IFERROR(VLOOKUP(E152,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G152" s="15">
-        <f>IF(B152="","",IFERROR(VLOOKUP(B152&amp;"_"&amp;C152,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B152="","",IFERROR(VLOOKUP(E152,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G152" s="13" t="n"/>
       <c r="H152" s="16">
         <f>IF(B152="","",IFERROR(VLOOKUP(B152,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -14589,7 +13468,7 @@
       </c>
       <c r="O152" s="20" t="n"/>
       <c r="P152" s="16">
-        <f>IF(B152="","",IFERROR(N152+VLOOKUP(E152,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B152="","",IFERROR(N152+VLOOKUP(E152,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q152" s="20" t="n"/>
@@ -14628,18 +13507,15 @@
       <c r="B153" s="13" t="n"/>
       <c r="C153" s="14" t="n"/>
       <c r="D153" s="15">
-        <f>IF(B153="","",IFERROR(VLOOKUP(C153,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B153="","",IFERROR(VLOOKUP(C153,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E153" s="14" t="n"/>
       <c r="F153" s="15">
-        <f>IF(B153="","",IFERROR(VLOOKUP(E153,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G153" s="15">
-        <f>IF(B153="","",IFERROR(VLOOKUP(B153&amp;"_"&amp;C153,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B153="","",IFERROR(VLOOKUP(E153,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G153" s="13" t="n"/>
       <c r="H153" s="16">
         <f>IF(B153="","",IFERROR(VLOOKUP(B153,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -14661,7 +13537,7 @@
       </c>
       <c r="O153" s="20" t="n"/>
       <c r="P153" s="16">
-        <f>IF(B153="","",IFERROR(N153+VLOOKUP(E153,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B153="","",IFERROR(N153+VLOOKUP(E153,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q153" s="20" t="n"/>
@@ -14700,18 +13576,15 @@
       <c r="B154" s="13" t="n"/>
       <c r="C154" s="14" t="n"/>
       <c r="D154" s="15">
-        <f>IF(B154="","",IFERROR(VLOOKUP(C154,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B154="","",IFERROR(VLOOKUP(C154,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E154" s="14" t="n"/>
       <c r="F154" s="15">
-        <f>IF(B154="","",IFERROR(VLOOKUP(E154,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G154" s="15">
-        <f>IF(B154="","",IFERROR(VLOOKUP(B154&amp;"_"&amp;C154,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B154="","",IFERROR(VLOOKUP(E154,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G154" s="13" t="n"/>
       <c r="H154" s="16">
         <f>IF(B154="","",IFERROR(VLOOKUP(B154,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -14733,7 +13606,7 @@
       </c>
       <c r="O154" s="20" t="n"/>
       <c r="P154" s="16">
-        <f>IF(B154="","",IFERROR(N154+VLOOKUP(E154,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B154="","",IFERROR(N154+VLOOKUP(E154,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q154" s="20" t="n"/>
@@ -14772,18 +13645,15 @@
       <c r="B155" s="13" t="n"/>
       <c r="C155" s="14" t="n"/>
       <c r="D155" s="15">
-        <f>IF(B155="","",IFERROR(VLOOKUP(C155,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B155="","",IFERROR(VLOOKUP(C155,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E155" s="14" t="n"/>
       <c r="F155" s="15">
-        <f>IF(B155="","",IFERROR(VLOOKUP(E155,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G155" s="15">
-        <f>IF(B155="","",IFERROR(VLOOKUP(B155&amp;"_"&amp;C155,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B155="","",IFERROR(VLOOKUP(E155,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G155" s="13" t="n"/>
       <c r="H155" s="16">
         <f>IF(B155="","",IFERROR(VLOOKUP(B155,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -14805,7 +13675,7 @@
       </c>
       <c r="O155" s="20" t="n"/>
       <c r="P155" s="16">
-        <f>IF(B155="","",IFERROR(N155+VLOOKUP(E155,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B155="","",IFERROR(N155+VLOOKUP(E155,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q155" s="20" t="n"/>
@@ -14844,18 +13714,15 @@
       <c r="B156" s="13" t="n"/>
       <c r="C156" s="14" t="n"/>
       <c r="D156" s="15">
-        <f>IF(B156="","",IFERROR(VLOOKUP(C156,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B156="","",IFERROR(VLOOKUP(C156,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E156" s="14" t="n"/>
       <c r="F156" s="15">
-        <f>IF(B156="","",IFERROR(VLOOKUP(E156,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G156" s="15">
-        <f>IF(B156="","",IFERROR(VLOOKUP(B156&amp;"_"&amp;C156,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B156="","",IFERROR(VLOOKUP(E156,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G156" s="13" t="n"/>
       <c r="H156" s="16">
         <f>IF(B156="","",IFERROR(VLOOKUP(B156,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -14877,7 +13744,7 @@
       </c>
       <c r="O156" s="20" t="n"/>
       <c r="P156" s="16">
-        <f>IF(B156="","",IFERROR(N156+VLOOKUP(E156,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B156="","",IFERROR(N156+VLOOKUP(E156,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q156" s="20" t="n"/>
@@ -14916,18 +13783,15 @@
       <c r="B157" s="13" t="n"/>
       <c r="C157" s="14" t="n"/>
       <c r="D157" s="15">
-        <f>IF(B157="","",IFERROR(VLOOKUP(C157,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B157="","",IFERROR(VLOOKUP(C157,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E157" s="14" t="n"/>
       <c r="F157" s="15">
-        <f>IF(B157="","",IFERROR(VLOOKUP(E157,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G157" s="15">
-        <f>IF(B157="","",IFERROR(VLOOKUP(B157&amp;"_"&amp;C157,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B157="","",IFERROR(VLOOKUP(E157,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G157" s="13" t="n"/>
       <c r="H157" s="16">
         <f>IF(B157="","",IFERROR(VLOOKUP(B157,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -14949,7 +13813,7 @@
       </c>
       <c r="O157" s="20" t="n"/>
       <c r="P157" s="16">
-        <f>IF(B157="","",IFERROR(N157+VLOOKUP(E157,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B157="","",IFERROR(N157+VLOOKUP(E157,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q157" s="20" t="n"/>
@@ -14988,18 +13852,15 @@
       <c r="B158" s="13" t="n"/>
       <c r="C158" s="14" t="n"/>
       <c r="D158" s="15">
-        <f>IF(B158="","",IFERROR(VLOOKUP(C158,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B158="","",IFERROR(VLOOKUP(C158,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E158" s="14" t="n"/>
       <c r="F158" s="15">
-        <f>IF(B158="","",IFERROR(VLOOKUP(E158,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G158" s="15">
-        <f>IF(B158="","",IFERROR(VLOOKUP(B158&amp;"_"&amp;C158,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B158="","",IFERROR(VLOOKUP(E158,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G158" s="13" t="n"/>
       <c r="H158" s="16">
         <f>IF(B158="","",IFERROR(VLOOKUP(B158,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -15021,7 +13882,7 @@
       </c>
       <c r="O158" s="20" t="n"/>
       <c r="P158" s="16">
-        <f>IF(B158="","",IFERROR(N158+VLOOKUP(E158,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B158="","",IFERROR(N158+VLOOKUP(E158,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q158" s="20" t="n"/>
@@ -15060,18 +13921,15 @@
       <c r="B159" s="13" t="n"/>
       <c r="C159" s="14" t="n"/>
       <c r="D159" s="15">
-        <f>IF(B159="","",IFERROR(VLOOKUP(C159,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B159="","",IFERROR(VLOOKUP(C159,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E159" s="14" t="n"/>
       <c r="F159" s="15">
-        <f>IF(B159="","",IFERROR(VLOOKUP(E159,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G159" s="15">
-        <f>IF(B159="","",IFERROR(VLOOKUP(B159&amp;"_"&amp;C159,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B159="","",IFERROR(VLOOKUP(E159,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G159" s="13" t="n"/>
       <c r="H159" s="16">
         <f>IF(B159="","",IFERROR(VLOOKUP(B159,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -15093,7 +13951,7 @@
       </c>
       <c r="O159" s="20" t="n"/>
       <c r="P159" s="16">
-        <f>IF(B159="","",IFERROR(N159+VLOOKUP(E159,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B159="","",IFERROR(N159+VLOOKUP(E159,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q159" s="20" t="n"/>
@@ -15132,18 +13990,15 @@
       <c r="B160" s="13" t="n"/>
       <c r="C160" s="14" t="n"/>
       <c r="D160" s="15">
-        <f>IF(B160="","",IFERROR(VLOOKUP(C160,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B160="","",IFERROR(VLOOKUP(C160,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E160" s="14" t="n"/>
       <c r="F160" s="15">
-        <f>IF(B160="","",IFERROR(VLOOKUP(E160,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G160" s="15">
-        <f>IF(B160="","",IFERROR(VLOOKUP(B160&amp;"_"&amp;C160,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B160="","",IFERROR(VLOOKUP(E160,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G160" s="13" t="n"/>
       <c r="H160" s="16">
         <f>IF(B160="","",IFERROR(VLOOKUP(B160,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -15165,7 +14020,7 @@
       </c>
       <c r="O160" s="20" t="n"/>
       <c r="P160" s="16">
-        <f>IF(B160="","",IFERROR(N160+VLOOKUP(E160,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B160="","",IFERROR(N160+VLOOKUP(E160,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q160" s="20" t="n"/>
@@ -15204,18 +14059,15 @@
       <c r="B161" s="13" t="n"/>
       <c r="C161" s="14" t="n"/>
       <c r="D161" s="15">
-        <f>IF(B161="","",IFERROR(VLOOKUP(C161,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B161="","",IFERROR(VLOOKUP(C161,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E161" s="14" t="n"/>
       <c r="F161" s="15">
-        <f>IF(B161="","",IFERROR(VLOOKUP(E161,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G161" s="15">
-        <f>IF(B161="","",IFERROR(VLOOKUP(B161&amp;"_"&amp;C161,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B161="","",IFERROR(VLOOKUP(E161,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G161" s="13" t="n"/>
       <c r="H161" s="16">
         <f>IF(B161="","",IFERROR(VLOOKUP(B161,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -15237,7 +14089,7 @@
       </c>
       <c r="O161" s="20" t="n"/>
       <c r="P161" s="16">
-        <f>IF(B161="","",IFERROR(N161+VLOOKUP(E161,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B161="","",IFERROR(N161+VLOOKUP(E161,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q161" s="20" t="n"/>
@@ -15276,18 +14128,15 @@
       <c r="B162" s="13" t="n"/>
       <c r="C162" s="14" t="n"/>
       <c r="D162" s="15">
-        <f>IF(B162="","",IFERROR(VLOOKUP(C162,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B162="","",IFERROR(VLOOKUP(C162,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E162" s="14" t="n"/>
       <c r="F162" s="15">
-        <f>IF(B162="","",IFERROR(VLOOKUP(E162,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G162" s="15">
-        <f>IF(B162="","",IFERROR(VLOOKUP(B162&amp;"_"&amp;C162,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B162="","",IFERROR(VLOOKUP(E162,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G162" s="13" t="n"/>
       <c r="H162" s="16">
         <f>IF(B162="","",IFERROR(VLOOKUP(B162,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -15309,7 +14158,7 @@
       </c>
       <c r="O162" s="20" t="n"/>
       <c r="P162" s="16">
-        <f>IF(B162="","",IFERROR(N162+VLOOKUP(E162,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B162="","",IFERROR(N162+VLOOKUP(E162,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q162" s="20" t="n"/>
@@ -15348,18 +14197,15 @@
       <c r="B163" s="13" t="n"/>
       <c r="C163" s="14" t="n"/>
       <c r="D163" s="15">
-        <f>IF(B163="","",IFERROR(VLOOKUP(C163,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B163="","",IFERROR(VLOOKUP(C163,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E163" s="14" t="n"/>
       <c r="F163" s="15">
-        <f>IF(B163="","",IFERROR(VLOOKUP(E163,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G163" s="15">
-        <f>IF(B163="","",IFERROR(VLOOKUP(B163&amp;"_"&amp;C163,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B163="","",IFERROR(VLOOKUP(E163,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G163" s="13" t="n"/>
       <c r="H163" s="16">
         <f>IF(B163="","",IFERROR(VLOOKUP(B163,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -15381,7 +14227,7 @@
       </c>
       <c r="O163" s="20" t="n"/>
       <c r="P163" s="16">
-        <f>IF(B163="","",IFERROR(N163+VLOOKUP(E163,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B163="","",IFERROR(N163+VLOOKUP(E163,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q163" s="20" t="n"/>
@@ -15420,18 +14266,15 @@
       <c r="B164" s="13" t="n"/>
       <c r="C164" s="14" t="n"/>
       <c r="D164" s="15">
-        <f>IF(B164="","",IFERROR(VLOOKUP(C164,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B164="","",IFERROR(VLOOKUP(C164,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E164" s="14" t="n"/>
       <c r="F164" s="15">
-        <f>IF(B164="","",IFERROR(VLOOKUP(E164,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G164" s="15">
-        <f>IF(B164="","",IFERROR(VLOOKUP(B164&amp;"_"&amp;C164,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B164="","",IFERROR(VLOOKUP(E164,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G164" s="13" t="n"/>
       <c r="H164" s="16">
         <f>IF(B164="","",IFERROR(VLOOKUP(B164,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -15453,7 +14296,7 @@
       </c>
       <c r="O164" s="20" t="n"/>
       <c r="P164" s="16">
-        <f>IF(B164="","",IFERROR(N164+VLOOKUP(E164,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B164="","",IFERROR(N164+VLOOKUP(E164,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q164" s="20" t="n"/>
@@ -15492,18 +14335,15 @@
       <c r="B165" s="13" t="n"/>
       <c r="C165" s="14" t="n"/>
       <c r="D165" s="15">
-        <f>IF(B165="","",IFERROR(VLOOKUP(C165,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B165="","",IFERROR(VLOOKUP(C165,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E165" s="14" t="n"/>
       <c r="F165" s="15">
-        <f>IF(B165="","",IFERROR(VLOOKUP(E165,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G165" s="15">
-        <f>IF(B165="","",IFERROR(VLOOKUP(B165&amp;"_"&amp;C165,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B165="","",IFERROR(VLOOKUP(E165,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G165" s="13" t="n"/>
       <c r="H165" s="16">
         <f>IF(B165="","",IFERROR(VLOOKUP(B165,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -15525,7 +14365,7 @@
       </c>
       <c r="O165" s="20" t="n"/>
       <c r="P165" s="16">
-        <f>IF(B165="","",IFERROR(N165+VLOOKUP(E165,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B165="","",IFERROR(N165+VLOOKUP(E165,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q165" s="20" t="n"/>
@@ -15564,18 +14404,15 @@
       <c r="B166" s="13" t="n"/>
       <c r="C166" s="14" t="n"/>
       <c r="D166" s="15">
-        <f>IF(B166="","",IFERROR(VLOOKUP(C166,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B166="","",IFERROR(VLOOKUP(C166,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E166" s="14" t="n"/>
       <c r="F166" s="15">
-        <f>IF(B166="","",IFERROR(VLOOKUP(E166,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G166" s="15">
-        <f>IF(B166="","",IFERROR(VLOOKUP(B166&amp;"_"&amp;C166,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B166="","",IFERROR(VLOOKUP(E166,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G166" s="13" t="n"/>
       <c r="H166" s="16">
         <f>IF(B166="","",IFERROR(VLOOKUP(B166,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -15597,7 +14434,7 @@
       </c>
       <c r="O166" s="20" t="n"/>
       <c r="P166" s="16">
-        <f>IF(B166="","",IFERROR(N166+VLOOKUP(E166,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B166="","",IFERROR(N166+VLOOKUP(E166,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q166" s="20" t="n"/>
@@ -15636,18 +14473,15 @@
       <c r="B167" s="13" t="n"/>
       <c r="C167" s="14" t="n"/>
       <c r="D167" s="15">
-        <f>IF(B167="","",IFERROR(VLOOKUP(C167,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B167="","",IFERROR(VLOOKUP(C167,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E167" s="14" t="n"/>
       <c r="F167" s="15">
-        <f>IF(B167="","",IFERROR(VLOOKUP(E167,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G167" s="15">
-        <f>IF(B167="","",IFERROR(VLOOKUP(B167&amp;"_"&amp;C167,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B167="","",IFERROR(VLOOKUP(E167,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G167" s="13" t="n"/>
       <c r="H167" s="16">
         <f>IF(B167="","",IFERROR(VLOOKUP(B167,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -15669,7 +14503,7 @@
       </c>
       <c r="O167" s="20" t="n"/>
       <c r="P167" s="16">
-        <f>IF(B167="","",IFERROR(N167+VLOOKUP(E167,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B167="","",IFERROR(N167+VLOOKUP(E167,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q167" s="20" t="n"/>
@@ -15708,18 +14542,15 @@
       <c r="B168" s="13" t="n"/>
       <c r="C168" s="14" t="n"/>
       <c r="D168" s="15">
-        <f>IF(B168="","",IFERROR(VLOOKUP(C168,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B168="","",IFERROR(VLOOKUP(C168,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E168" s="14" t="n"/>
       <c r="F168" s="15">
-        <f>IF(B168="","",IFERROR(VLOOKUP(E168,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G168" s="15">
-        <f>IF(B168="","",IFERROR(VLOOKUP(B168&amp;"_"&amp;C168,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B168="","",IFERROR(VLOOKUP(E168,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G168" s="13" t="n"/>
       <c r="H168" s="16">
         <f>IF(B168="","",IFERROR(VLOOKUP(B168,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -15741,7 +14572,7 @@
       </c>
       <c r="O168" s="20" t="n"/>
       <c r="P168" s="16">
-        <f>IF(B168="","",IFERROR(N168+VLOOKUP(E168,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B168="","",IFERROR(N168+VLOOKUP(E168,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q168" s="20" t="n"/>
@@ -15780,18 +14611,15 @@
       <c r="B169" s="13" t="n"/>
       <c r="C169" s="14" t="n"/>
       <c r="D169" s="15">
-        <f>IF(B169="","",IFERROR(VLOOKUP(C169,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B169="","",IFERROR(VLOOKUP(C169,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E169" s="14" t="n"/>
       <c r="F169" s="15">
-        <f>IF(B169="","",IFERROR(VLOOKUP(E169,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G169" s="15">
-        <f>IF(B169="","",IFERROR(VLOOKUP(B169&amp;"_"&amp;C169,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B169="","",IFERROR(VLOOKUP(E169,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G169" s="13" t="n"/>
       <c r="H169" s="16">
         <f>IF(B169="","",IFERROR(VLOOKUP(B169,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -15813,7 +14641,7 @@
       </c>
       <c r="O169" s="20" t="n"/>
       <c r="P169" s="16">
-        <f>IF(B169="","",IFERROR(N169+VLOOKUP(E169,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B169="","",IFERROR(N169+VLOOKUP(E169,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q169" s="20" t="n"/>
@@ -15852,18 +14680,15 @@
       <c r="B170" s="13" t="n"/>
       <c r="C170" s="14" t="n"/>
       <c r="D170" s="15">
-        <f>IF(B170="","",IFERROR(VLOOKUP(C170,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B170="","",IFERROR(VLOOKUP(C170,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E170" s="14" t="n"/>
       <c r="F170" s="15">
-        <f>IF(B170="","",IFERROR(VLOOKUP(E170,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G170" s="15">
-        <f>IF(B170="","",IFERROR(VLOOKUP(B170&amp;"_"&amp;C170,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B170="","",IFERROR(VLOOKUP(E170,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G170" s="13" t="n"/>
       <c r="H170" s="16">
         <f>IF(B170="","",IFERROR(VLOOKUP(B170,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -15885,7 +14710,7 @@
       </c>
       <c r="O170" s="20" t="n"/>
       <c r="P170" s="16">
-        <f>IF(B170="","",IFERROR(N170+VLOOKUP(E170,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B170="","",IFERROR(N170+VLOOKUP(E170,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q170" s="20" t="n"/>
@@ -15924,18 +14749,15 @@
       <c r="B171" s="13" t="n"/>
       <c r="C171" s="14" t="n"/>
       <c r="D171" s="15">
-        <f>IF(B171="","",IFERROR(VLOOKUP(C171,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B171="","",IFERROR(VLOOKUP(C171,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E171" s="14" t="n"/>
       <c r="F171" s="15">
-        <f>IF(B171="","",IFERROR(VLOOKUP(E171,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G171" s="15">
-        <f>IF(B171="","",IFERROR(VLOOKUP(B171&amp;"_"&amp;C171,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B171="","",IFERROR(VLOOKUP(E171,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G171" s="13" t="n"/>
       <c r="H171" s="16">
         <f>IF(B171="","",IFERROR(VLOOKUP(B171,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -15957,7 +14779,7 @@
       </c>
       <c r="O171" s="20" t="n"/>
       <c r="P171" s="16">
-        <f>IF(B171="","",IFERROR(N171+VLOOKUP(E171,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B171="","",IFERROR(N171+VLOOKUP(E171,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q171" s="20" t="n"/>
@@ -15996,18 +14818,15 @@
       <c r="B172" s="13" t="n"/>
       <c r="C172" s="14" t="n"/>
       <c r="D172" s="15">
-        <f>IF(B172="","",IFERROR(VLOOKUP(C172,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B172="","",IFERROR(VLOOKUP(C172,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E172" s="14" t="n"/>
       <c r="F172" s="15">
-        <f>IF(B172="","",IFERROR(VLOOKUP(E172,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G172" s="15">
-        <f>IF(B172="","",IFERROR(VLOOKUP(B172&amp;"_"&amp;C172,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B172="","",IFERROR(VLOOKUP(E172,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G172" s="13" t="n"/>
       <c r="H172" s="16">
         <f>IF(B172="","",IFERROR(VLOOKUP(B172,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -16029,7 +14848,7 @@
       </c>
       <c r="O172" s="20" t="n"/>
       <c r="P172" s="16">
-        <f>IF(B172="","",IFERROR(N172+VLOOKUP(E172,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B172="","",IFERROR(N172+VLOOKUP(E172,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q172" s="20" t="n"/>
@@ -16068,18 +14887,15 @@
       <c r="B173" s="13" t="n"/>
       <c r="C173" s="14" t="n"/>
       <c r="D173" s="15">
-        <f>IF(B173="","",IFERROR(VLOOKUP(C173,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B173="","",IFERROR(VLOOKUP(C173,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E173" s="14" t="n"/>
       <c r="F173" s="15">
-        <f>IF(B173="","",IFERROR(VLOOKUP(E173,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G173" s="15">
-        <f>IF(B173="","",IFERROR(VLOOKUP(B173&amp;"_"&amp;C173,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B173="","",IFERROR(VLOOKUP(E173,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G173" s="13" t="n"/>
       <c r="H173" s="16">
         <f>IF(B173="","",IFERROR(VLOOKUP(B173,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -16101,7 +14917,7 @@
       </c>
       <c r="O173" s="20" t="n"/>
       <c r="P173" s="16">
-        <f>IF(B173="","",IFERROR(N173+VLOOKUP(E173,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B173="","",IFERROR(N173+VLOOKUP(E173,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q173" s="20" t="n"/>
@@ -16140,18 +14956,15 @@
       <c r="B174" s="13" t="n"/>
       <c r="C174" s="14" t="n"/>
       <c r="D174" s="15">
-        <f>IF(B174="","",IFERROR(VLOOKUP(C174,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B174="","",IFERROR(VLOOKUP(C174,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E174" s="14" t="n"/>
       <c r="F174" s="15">
-        <f>IF(B174="","",IFERROR(VLOOKUP(E174,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G174" s="15">
-        <f>IF(B174="","",IFERROR(VLOOKUP(B174&amp;"_"&amp;C174,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B174="","",IFERROR(VLOOKUP(E174,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G174" s="13" t="n"/>
       <c r="H174" s="16">
         <f>IF(B174="","",IFERROR(VLOOKUP(B174,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -16173,7 +14986,7 @@
       </c>
       <c r="O174" s="20" t="n"/>
       <c r="P174" s="16">
-        <f>IF(B174="","",IFERROR(N174+VLOOKUP(E174,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B174="","",IFERROR(N174+VLOOKUP(E174,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q174" s="20" t="n"/>
@@ -16212,18 +15025,15 @@
       <c r="B175" s="13" t="n"/>
       <c r="C175" s="14" t="n"/>
       <c r="D175" s="15">
-        <f>IF(B175="","",IFERROR(VLOOKUP(C175,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B175="","",IFERROR(VLOOKUP(C175,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E175" s="14" t="n"/>
       <c r="F175" s="15">
-        <f>IF(B175="","",IFERROR(VLOOKUP(E175,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G175" s="15">
-        <f>IF(B175="","",IFERROR(VLOOKUP(B175&amp;"_"&amp;C175,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B175="","",IFERROR(VLOOKUP(E175,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G175" s="13" t="n"/>
       <c r="H175" s="16">
         <f>IF(B175="","",IFERROR(VLOOKUP(B175,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -16245,7 +15055,7 @@
       </c>
       <c r="O175" s="20" t="n"/>
       <c r="P175" s="16">
-        <f>IF(B175="","",IFERROR(N175+VLOOKUP(E175,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B175="","",IFERROR(N175+VLOOKUP(E175,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q175" s="20" t="n"/>
@@ -16284,18 +15094,15 @@
       <c r="B176" s="13" t="n"/>
       <c r="C176" s="14" t="n"/>
       <c r="D176" s="15">
-        <f>IF(B176="","",IFERROR(VLOOKUP(C176,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B176="","",IFERROR(VLOOKUP(C176,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E176" s="14" t="n"/>
       <c r="F176" s="15">
-        <f>IF(B176="","",IFERROR(VLOOKUP(E176,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G176" s="15">
-        <f>IF(B176="","",IFERROR(VLOOKUP(B176&amp;"_"&amp;C176,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B176="","",IFERROR(VLOOKUP(E176,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G176" s="13" t="n"/>
       <c r="H176" s="16">
         <f>IF(B176="","",IFERROR(VLOOKUP(B176,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -16317,7 +15124,7 @@
       </c>
       <c r="O176" s="20" t="n"/>
       <c r="P176" s="16">
-        <f>IF(B176="","",IFERROR(N176+VLOOKUP(E176,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B176="","",IFERROR(N176+VLOOKUP(E176,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q176" s="20" t="n"/>
@@ -16356,18 +15163,15 @@
       <c r="B177" s="13" t="n"/>
       <c r="C177" s="14" t="n"/>
       <c r="D177" s="15">
-        <f>IF(B177="","",IFERROR(VLOOKUP(C177,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B177="","",IFERROR(VLOOKUP(C177,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E177" s="14" t="n"/>
       <c r="F177" s="15">
-        <f>IF(B177="","",IFERROR(VLOOKUP(E177,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G177" s="15">
-        <f>IF(B177="","",IFERROR(VLOOKUP(B177&amp;"_"&amp;C177,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B177="","",IFERROR(VLOOKUP(E177,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G177" s="13" t="n"/>
       <c r="H177" s="16">
         <f>IF(B177="","",IFERROR(VLOOKUP(B177,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -16389,7 +15193,7 @@
       </c>
       <c r="O177" s="20" t="n"/>
       <c r="P177" s="16">
-        <f>IF(B177="","",IFERROR(N177+VLOOKUP(E177,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B177="","",IFERROR(N177+VLOOKUP(E177,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q177" s="20" t="n"/>
@@ -16428,18 +15232,15 @@
       <c r="B178" s="13" t="n"/>
       <c r="C178" s="14" t="n"/>
       <c r="D178" s="15">
-        <f>IF(B178="","",IFERROR(VLOOKUP(C178,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B178="","",IFERROR(VLOOKUP(C178,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E178" s="14" t="n"/>
       <c r="F178" s="15">
-        <f>IF(B178="","",IFERROR(VLOOKUP(E178,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G178" s="15">
-        <f>IF(B178="","",IFERROR(VLOOKUP(B178&amp;"_"&amp;C178,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B178="","",IFERROR(VLOOKUP(E178,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G178" s="13" t="n"/>
       <c r="H178" s="16">
         <f>IF(B178="","",IFERROR(VLOOKUP(B178,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -16461,7 +15262,7 @@
       </c>
       <c r="O178" s="20" t="n"/>
       <c r="P178" s="16">
-        <f>IF(B178="","",IFERROR(N178+VLOOKUP(E178,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B178="","",IFERROR(N178+VLOOKUP(E178,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q178" s="20" t="n"/>
@@ -16500,18 +15301,15 @@
       <c r="B179" s="13" t="n"/>
       <c r="C179" s="14" t="n"/>
       <c r="D179" s="15">
-        <f>IF(B179="","",IFERROR(VLOOKUP(C179,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B179="","",IFERROR(VLOOKUP(C179,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E179" s="14" t="n"/>
       <c r="F179" s="15">
-        <f>IF(B179="","",IFERROR(VLOOKUP(E179,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G179" s="15">
-        <f>IF(B179="","",IFERROR(VLOOKUP(B179&amp;"_"&amp;C179,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B179="","",IFERROR(VLOOKUP(E179,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G179" s="13" t="n"/>
       <c r="H179" s="16">
         <f>IF(B179="","",IFERROR(VLOOKUP(B179,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -16533,7 +15331,7 @@
       </c>
       <c r="O179" s="20" t="n"/>
       <c r="P179" s="16">
-        <f>IF(B179="","",IFERROR(N179+VLOOKUP(E179,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B179="","",IFERROR(N179+VLOOKUP(E179,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q179" s="20" t="n"/>
@@ -16572,18 +15370,15 @@
       <c r="B180" s="13" t="n"/>
       <c r="C180" s="14" t="n"/>
       <c r="D180" s="15">
-        <f>IF(B180="","",IFERROR(VLOOKUP(C180,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B180="","",IFERROR(VLOOKUP(C180,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E180" s="14" t="n"/>
       <c r="F180" s="15">
-        <f>IF(B180="","",IFERROR(VLOOKUP(E180,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G180" s="15">
-        <f>IF(B180="","",IFERROR(VLOOKUP(B180&amp;"_"&amp;C180,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B180="","",IFERROR(VLOOKUP(E180,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G180" s="13" t="n"/>
       <c r="H180" s="16">
         <f>IF(B180="","",IFERROR(VLOOKUP(B180,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -16605,7 +15400,7 @@
       </c>
       <c r="O180" s="20" t="n"/>
       <c r="P180" s="16">
-        <f>IF(B180="","",IFERROR(N180+VLOOKUP(E180,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B180="","",IFERROR(N180+VLOOKUP(E180,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q180" s="20" t="n"/>
@@ -16644,18 +15439,15 @@
       <c r="B181" s="13" t="n"/>
       <c r="C181" s="14" t="n"/>
       <c r="D181" s="15">
-        <f>IF(B181="","",IFERROR(VLOOKUP(C181,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B181="","",IFERROR(VLOOKUP(C181,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E181" s="14" t="n"/>
       <c r="F181" s="15">
-        <f>IF(B181="","",IFERROR(VLOOKUP(E181,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G181" s="15">
-        <f>IF(B181="","",IFERROR(VLOOKUP(B181&amp;"_"&amp;C181,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B181="","",IFERROR(VLOOKUP(E181,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G181" s="13" t="n"/>
       <c r="H181" s="16">
         <f>IF(B181="","",IFERROR(VLOOKUP(B181,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -16677,7 +15469,7 @@
       </c>
       <c r="O181" s="20" t="n"/>
       <c r="P181" s="16">
-        <f>IF(B181="","",IFERROR(N181+VLOOKUP(E181,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B181="","",IFERROR(N181+VLOOKUP(E181,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q181" s="20" t="n"/>
@@ -16716,18 +15508,15 @@
       <c r="B182" s="13" t="n"/>
       <c r="C182" s="14" t="n"/>
       <c r="D182" s="15">
-        <f>IF(B182="","",IFERROR(VLOOKUP(C182,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B182="","",IFERROR(VLOOKUP(C182,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E182" s="14" t="n"/>
       <c r="F182" s="15">
-        <f>IF(B182="","",IFERROR(VLOOKUP(E182,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G182" s="15">
-        <f>IF(B182="","",IFERROR(VLOOKUP(B182&amp;"_"&amp;C182,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B182="","",IFERROR(VLOOKUP(E182,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G182" s="13" t="n"/>
       <c r="H182" s="16">
         <f>IF(B182="","",IFERROR(VLOOKUP(B182,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -16749,7 +15538,7 @@
       </c>
       <c r="O182" s="20" t="n"/>
       <c r="P182" s="16">
-        <f>IF(B182="","",IFERROR(N182+VLOOKUP(E182,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B182="","",IFERROR(N182+VLOOKUP(E182,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q182" s="20" t="n"/>
@@ -16788,18 +15577,15 @@
       <c r="B183" s="13" t="n"/>
       <c r="C183" s="14" t="n"/>
       <c r="D183" s="15">
-        <f>IF(B183="","",IFERROR(VLOOKUP(C183,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B183="","",IFERROR(VLOOKUP(C183,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E183" s="14" t="n"/>
       <c r="F183" s="15">
-        <f>IF(B183="","",IFERROR(VLOOKUP(E183,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G183" s="15">
-        <f>IF(B183="","",IFERROR(VLOOKUP(B183&amp;"_"&amp;C183,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B183="","",IFERROR(VLOOKUP(E183,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G183" s="13" t="n"/>
       <c r="H183" s="16">
         <f>IF(B183="","",IFERROR(VLOOKUP(B183,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -16821,7 +15607,7 @@
       </c>
       <c r="O183" s="20" t="n"/>
       <c r="P183" s="16">
-        <f>IF(B183="","",IFERROR(N183+VLOOKUP(E183,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B183="","",IFERROR(N183+VLOOKUP(E183,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q183" s="20" t="n"/>
@@ -16860,18 +15646,15 @@
       <c r="B184" s="13" t="n"/>
       <c r="C184" s="14" t="n"/>
       <c r="D184" s="15">
-        <f>IF(B184="","",IFERROR(VLOOKUP(C184,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B184="","",IFERROR(VLOOKUP(C184,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E184" s="14" t="n"/>
       <c r="F184" s="15">
-        <f>IF(B184="","",IFERROR(VLOOKUP(E184,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G184" s="15">
-        <f>IF(B184="","",IFERROR(VLOOKUP(B184&amp;"_"&amp;C184,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B184="","",IFERROR(VLOOKUP(E184,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G184" s="13" t="n"/>
       <c r="H184" s="16">
         <f>IF(B184="","",IFERROR(VLOOKUP(B184,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -16893,7 +15676,7 @@
       </c>
       <c r="O184" s="20" t="n"/>
       <c r="P184" s="16">
-        <f>IF(B184="","",IFERROR(N184+VLOOKUP(E184,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B184="","",IFERROR(N184+VLOOKUP(E184,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q184" s="20" t="n"/>
@@ -16932,18 +15715,15 @@
       <c r="B185" s="13" t="n"/>
       <c r="C185" s="14" t="n"/>
       <c r="D185" s="15">
-        <f>IF(B185="","",IFERROR(VLOOKUP(C185,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B185="","",IFERROR(VLOOKUP(C185,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E185" s="14" t="n"/>
       <c r="F185" s="15">
-        <f>IF(B185="","",IFERROR(VLOOKUP(E185,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G185" s="15">
-        <f>IF(B185="","",IFERROR(VLOOKUP(B185&amp;"_"&amp;C185,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B185="","",IFERROR(VLOOKUP(E185,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G185" s="13" t="n"/>
       <c r="H185" s="16">
         <f>IF(B185="","",IFERROR(VLOOKUP(B185,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -16965,7 +15745,7 @@
       </c>
       <c r="O185" s="20" t="n"/>
       <c r="P185" s="16">
-        <f>IF(B185="","",IFERROR(N185+VLOOKUP(E185,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B185="","",IFERROR(N185+VLOOKUP(E185,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q185" s="20" t="n"/>
@@ -17004,18 +15784,15 @@
       <c r="B186" s="13" t="n"/>
       <c r="C186" s="14" t="n"/>
       <c r="D186" s="15">
-        <f>IF(B186="","",IFERROR(VLOOKUP(C186,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B186="","",IFERROR(VLOOKUP(C186,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E186" s="14" t="n"/>
       <c r="F186" s="15">
-        <f>IF(B186="","",IFERROR(VLOOKUP(E186,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G186" s="15">
-        <f>IF(B186="","",IFERROR(VLOOKUP(B186&amp;"_"&amp;C186,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B186="","",IFERROR(VLOOKUP(E186,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G186" s="13" t="n"/>
       <c r="H186" s="16">
         <f>IF(B186="","",IFERROR(VLOOKUP(B186,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -17037,7 +15814,7 @@
       </c>
       <c r="O186" s="20" t="n"/>
       <c r="P186" s="16">
-        <f>IF(B186="","",IFERROR(N186+VLOOKUP(E186,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B186="","",IFERROR(N186+VLOOKUP(E186,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q186" s="20" t="n"/>
@@ -17076,18 +15853,15 @@
       <c r="B187" s="13" t="n"/>
       <c r="C187" s="14" t="n"/>
       <c r="D187" s="15">
-        <f>IF(B187="","",IFERROR(VLOOKUP(C187,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B187="","",IFERROR(VLOOKUP(C187,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E187" s="14" t="n"/>
       <c r="F187" s="15">
-        <f>IF(B187="","",IFERROR(VLOOKUP(E187,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G187" s="15">
-        <f>IF(B187="","",IFERROR(VLOOKUP(B187&amp;"_"&amp;C187,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B187="","",IFERROR(VLOOKUP(E187,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G187" s="13" t="n"/>
       <c r="H187" s="16">
         <f>IF(B187="","",IFERROR(VLOOKUP(B187,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -17109,7 +15883,7 @@
       </c>
       <c r="O187" s="20" t="n"/>
       <c r="P187" s="16">
-        <f>IF(B187="","",IFERROR(N187+VLOOKUP(E187,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B187="","",IFERROR(N187+VLOOKUP(E187,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q187" s="20" t="n"/>
@@ -17148,18 +15922,15 @@
       <c r="B188" s="13" t="n"/>
       <c r="C188" s="14" t="n"/>
       <c r="D188" s="15">
-        <f>IF(B188="","",IFERROR(VLOOKUP(C188,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B188="","",IFERROR(VLOOKUP(C188,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E188" s="14" t="n"/>
       <c r="F188" s="15">
-        <f>IF(B188="","",IFERROR(VLOOKUP(E188,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G188" s="15">
-        <f>IF(B188="","",IFERROR(VLOOKUP(B188&amp;"_"&amp;C188,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B188="","",IFERROR(VLOOKUP(E188,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G188" s="13" t="n"/>
       <c r="H188" s="16">
         <f>IF(B188="","",IFERROR(VLOOKUP(B188,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -17181,7 +15952,7 @@
       </c>
       <c r="O188" s="20" t="n"/>
       <c r="P188" s="16">
-        <f>IF(B188="","",IFERROR(N188+VLOOKUP(E188,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B188="","",IFERROR(N188+VLOOKUP(E188,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q188" s="20" t="n"/>
@@ -17220,18 +15991,15 @@
       <c r="B189" s="13" t="n"/>
       <c r="C189" s="14" t="n"/>
       <c r="D189" s="15">
-        <f>IF(B189="","",IFERROR(VLOOKUP(C189,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B189="","",IFERROR(VLOOKUP(C189,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E189" s="14" t="n"/>
       <c r="F189" s="15">
-        <f>IF(B189="","",IFERROR(VLOOKUP(E189,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G189" s="15">
-        <f>IF(B189="","",IFERROR(VLOOKUP(B189&amp;"_"&amp;C189,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B189="","",IFERROR(VLOOKUP(E189,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G189" s="13" t="n"/>
       <c r="H189" s="16">
         <f>IF(B189="","",IFERROR(VLOOKUP(B189,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -17253,7 +16021,7 @@
       </c>
       <c r="O189" s="20" t="n"/>
       <c r="P189" s="16">
-        <f>IF(B189="","",IFERROR(N189+VLOOKUP(E189,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B189="","",IFERROR(N189+VLOOKUP(E189,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q189" s="20" t="n"/>
@@ -17292,18 +16060,15 @@
       <c r="B190" s="13" t="n"/>
       <c r="C190" s="14" t="n"/>
       <c r="D190" s="15">
-        <f>IF(B190="","",IFERROR(VLOOKUP(C190,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B190="","",IFERROR(VLOOKUP(C190,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E190" s="14" t="n"/>
       <c r="F190" s="15">
-        <f>IF(B190="","",IFERROR(VLOOKUP(E190,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G190" s="15">
-        <f>IF(B190="","",IFERROR(VLOOKUP(B190&amp;"_"&amp;C190,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B190="","",IFERROR(VLOOKUP(E190,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G190" s="13" t="n"/>
       <c r="H190" s="16">
         <f>IF(B190="","",IFERROR(VLOOKUP(B190,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -17325,7 +16090,7 @@
       </c>
       <c r="O190" s="20" t="n"/>
       <c r="P190" s="16">
-        <f>IF(B190="","",IFERROR(N190+VLOOKUP(E190,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B190="","",IFERROR(N190+VLOOKUP(E190,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q190" s="20" t="n"/>
@@ -17364,18 +16129,15 @@
       <c r="B191" s="13" t="n"/>
       <c r="C191" s="14" t="n"/>
       <c r="D191" s="15">
-        <f>IF(B191="","",IFERROR(VLOOKUP(C191,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B191="","",IFERROR(VLOOKUP(C191,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E191" s="14" t="n"/>
       <c r="F191" s="15">
-        <f>IF(B191="","",IFERROR(VLOOKUP(E191,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G191" s="15">
-        <f>IF(B191="","",IFERROR(VLOOKUP(B191&amp;"_"&amp;C191,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B191="","",IFERROR(VLOOKUP(E191,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G191" s="13" t="n"/>
       <c r="H191" s="16">
         <f>IF(B191="","",IFERROR(VLOOKUP(B191,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -17397,7 +16159,7 @@
       </c>
       <c r="O191" s="20" t="n"/>
       <c r="P191" s="16">
-        <f>IF(B191="","",IFERROR(N191+VLOOKUP(E191,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B191="","",IFERROR(N191+VLOOKUP(E191,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q191" s="20" t="n"/>
@@ -17436,18 +16198,15 @@
       <c r="B192" s="13" t="n"/>
       <c r="C192" s="14" t="n"/>
       <c r="D192" s="15">
-        <f>IF(B192="","",IFERROR(VLOOKUP(C192,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B192="","",IFERROR(VLOOKUP(C192,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E192" s="14" t="n"/>
       <c r="F192" s="15">
-        <f>IF(B192="","",IFERROR(VLOOKUP(E192,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G192" s="15">
-        <f>IF(B192="","",IFERROR(VLOOKUP(B192&amp;"_"&amp;C192,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B192="","",IFERROR(VLOOKUP(E192,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G192" s="13" t="n"/>
       <c r="H192" s="16">
         <f>IF(B192="","",IFERROR(VLOOKUP(B192,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -17469,7 +16228,7 @@
       </c>
       <c r="O192" s="20" t="n"/>
       <c r="P192" s="16">
-        <f>IF(B192="","",IFERROR(N192+VLOOKUP(E192,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B192="","",IFERROR(N192+VLOOKUP(E192,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q192" s="20" t="n"/>
@@ -17508,18 +16267,15 @@
       <c r="B193" s="13" t="n"/>
       <c r="C193" s="14" t="n"/>
       <c r="D193" s="15">
-        <f>IF(B193="","",IFERROR(VLOOKUP(C193,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B193="","",IFERROR(VLOOKUP(C193,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E193" s="14" t="n"/>
       <c r="F193" s="15">
-        <f>IF(B193="","",IFERROR(VLOOKUP(E193,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G193" s="15">
-        <f>IF(B193="","",IFERROR(VLOOKUP(B193&amp;"_"&amp;C193,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B193="","",IFERROR(VLOOKUP(E193,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G193" s="13" t="n"/>
       <c r="H193" s="16">
         <f>IF(B193="","",IFERROR(VLOOKUP(B193,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -17541,7 +16297,7 @@
       </c>
       <c r="O193" s="20" t="n"/>
       <c r="P193" s="16">
-        <f>IF(B193="","",IFERROR(N193+VLOOKUP(E193,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B193="","",IFERROR(N193+VLOOKUP(E193,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q193" s="20" t="n"/>
@@ -17580,18 +16336,15 @@
       <c r="B194" s="13" t="n"/>
       <c r="C194" s="14" t="n"/>
       <c r="D194" s="15">
-        <f>IF(B194="","",IFERROR(VLOOKUP(C194,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B194="","",IFERROR(VLOOKUP(C194,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E194" s="14" t="n"/>
       <c r="F194" s="15">
-        <f>IF(B194="","",IFERROR(VLOOKUP(E194,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G194" s="15">
-        <f>IF(B194="","",IFERROR(VLOOKUP(B194&amp;"_"&amp;C194,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B194="","",IFERROR(VLOOKUP(E194,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G194" s="13" t="n"/>
       <c r="H194" s="16">
         <f>IF(B194="","",IFERROR(VLOOKUP(B194,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -17613,7 +16366,7 @@
       </c>
       <c r="O194" s="20" t="n"/>
       <c r="P194" s="16">
-        <f>IF(B194="","",IFERROR(N194+VLOOKUP(E194,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B194="","",IFERROR(N194+VLOOKUP(E194,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q194" s="20" t="n"/>
@@ -17652,18 +16405,15 @@
       <c r="B195" s="13" t="n"/>
       <c r="C195" s="14" t="n"/>
       <c r="D195" s="15">
-        <f>IF(B195="","",IFERROR(VLOOKUP(C195,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B195="","",IFERROR(VLOOKUP(C195,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E195" s="14" t="n"/>
       <c r="F195" s="15">
-        <f>IF(B195="","",IFERROR(VLOOKUP(E195,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G195" s="15">
-        <f>IF(B195="","",IFERROR(VLOOKUP(B195&amp;"_"&amp;C195,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B195="","",IFERROR(VLOOKUP(E195,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G195" s="13" t="n"/>
       <c r="H195" s="16">
         <f>IF(B195="","",IFERROR(VLOOKUP(B195,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -17685,7 +16435,7 @@
       </c>
       <c r="O195" s="20" t="n"/>
       <c r="P195" s="16">
-        <f>IF(B195="","",IFERROR(N195+VLOOKUP(E195,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B195="","",IFERROR(N195+VLOOKUP(E195,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q195" s="20" t="n"/>
@@ -17724,18 +16474,15 @@
       <c r="B196" s="13" t="n"/>
       <c r="C196" s="14" t="n"/>
       <c r="D196" s="15">
-        <f>IF(B196="","",IFERROR(VLOOKUP(C196,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B196="","",IFERROR(VLOOKUP(C196,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E196" s="14" t="n"/>
       <c r="F196" s="15">
-        <f>IF(B196="","",IFERROR(VLOOKUP(E196,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G196" s="15">
-        <f>IF(B196="","",IFERROR(VLOOKUP(B196&amp;"_"&amp;C196,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B196="","",IFERROR(VLOOKUP(E196,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G196" s="13" t="n"/>
       <c r="H196" s="16">
         <f>IF(B196="","",IFERROR(VLOOKUP(B196,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -17757,7 +16504,7 @@
       </c>
       <c r="O196" s="20" t="n"/>
       <c r="P196" s="16">
-        <f>IF(B196="","",IFERROR(N196+VLOOKUP(E196,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B196="","",IFERROR(N196+VLOOKUP(E196,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q196" s="20" t="n"/>
@@ -17796,18 +16543,15 @@
       <c r="B197" s="13" t="n"/>
       <c r="C197" s="14" t="n"/>
       <c r="D197" s="15">
-        <f>IF(B197="","",IFERROR(VLOOKUP(C197,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B197="","",IFERROR(VLOOKUP(C197,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E197" s="14" t="n"/>
       <c r="F197" s="15">
-        <f>IF(B197="","",IFERROR(VLOOKUP(E197,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G197" s="15">
-        <f>IF(B197="","",IFERROR(VLOOKUP(B197&amp;"_"&amp;C197,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B197="","",IFERROR(VLOOKUP(E197,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G197" s="13" t="n"/>
       <c r="H197" s="16">
         <f>IF(B197="","",IFERROR(VLOOKUP(B197,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -17829,7 +16573,7 @@
       </c>
       <c r="O197" s="20" t="n"/>
       <c r="P197" s="16">
-        <f>IF(B197="","",IFERROR(N197+VLOOKUP(E197,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B197="","",IFERROR(N197+VLOOKUP(E197,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q197" s="20" t="n"/>
@@ -17868,18 +16612,15 @@
       <c r="B198" s="13" t="n"/>
       <c r="C198" s="14" t="n"/>
       <c r="D198" s="15">
-        <f>IF(B198="","",IFERROR(VLOOKUP(C198,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B198="","",IFERROR(VLOOKUP(C198,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E198" s="14" t="n"/>
       <c r="F198" s="15">
-        <f>IF(B198="","",IFERROR(VLOOKUP(E198,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G198" s="15">
-        <f>IF(B198="","",IFERROR(VLOOKUP(B198&amp;"_"&amp;C198,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B198="","",IFERROR(VLOOKUP(E198,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G198" s="13" t="n"/>
       <c r="H198" s="16">
         <f>IF(B198="","",IFERROR(VLOOKUP(B198,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -17901,7 +16642,7 @@
       </c>
       <c r="O198" s="20" t="n"/>
       <c r="P198" s="16">
-        <f>IF(B198="","",IFERROR(N198+VLOOKUP(E198,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B198="","",IFERROR(N198+VLOOKUP(E198,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q198" s="20" t="n"/>
@@ -17940,18 +16681,15 @@
       <c r="B199" s="13" t="n"/>
       <c r="C199" s="14" t="n"/>
       <c r="D199" s="15">
-        <f>IF(B199="","",IFERROR(VLOOKUP(C199,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B199="","",IFERROR(VLOOKUP(C199,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E199" s="14" t="n"/>
       <c r="F199" s="15">
-        <f>IF(B199="","",IFERROR(VLOOKUP(E199,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G199" s="15">
-        <f>IF(B199="","",IFERROR(VLOOKUP(B199&amp;"_"&amp;C199,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B199="","",IFERROR(VLOOKUP(E199,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G199" s="13" t="n"/>
       <c r="H199" s="16">
         <f>IF(B199="","",IFERROR(VLOOKUP(B199,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -17973,7 +16711,7 @@
       </c>
       <c r="O199" s="20" t="n"/>
       <c r="P199" s="16">
-        <f>IF(B199="","",IFERROR(N199+VLOOKUP(E199,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B199="","",IFERROR(N199+VLOOKUP(E199,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q199" s="20" t="n"/>
@@ -18012,18 +16750,15 @@
       <c r="B200" s="13" t="n"/>
       <c r="C200" s="14" t="n"/>
       <c r="D200" s="15">
-        <f>IF(B200="","",IFERROR(VLOOKUP(C200,'Reference Data 기준데이터'!$E$8:$F$30,2,FALSE),""))</f>
+        <f>IF(B200="","",IFERROR(VLOOKUP(C200,'Reference Data 기준데이터'!$A$26:$B$32,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="E200" s="14" t="n"/>
       <c r="F200" s="15">
-        <f>IF(B200="","",IFERROR(VLOOKUP(E200,'Reference Data 기준데이터'!$A$8:$F$30,2,FALSE),""))</f>
-        <v/>
-      </c>
-      <c r="G200" s="15">
-        <f>IF(B200="","",IFERROR(VLOOKUP(B200&amp;"_"&amp;C200,'Reference Data 기준데이터'!$A$33:$B$51,2,FALSE),""))</f>
-        <v/>
-      </c>
+        <f>IF(B200="","",IFERROR(VLOOKUP(E200,'Reference Data 기준데이터'!$A$8:$D$23,2,FALSE),""))</f>
+        <v/>
+      </c>
+      <c r="G200" s="13" t="n"/>
       <c r="H200" s="16">
         <f>IF(B200="","",IFERROR(VLOOKUP(B200,'Reference Data 기준데이터'!$A$2:$J$5,3,FALSE),""))</f>
         <v/>
@@ -18045,7 +16780,7 @@
       </c>
       <c r="O200" s="20" t="n"/>
       <c r="P200" s="16">
-        <f>IF(B200="","",IFERROR(N200+VLOOKUP(E200,'Reference Data 기준데이터'!$A$8:$F$30,4,FALSE),""))</f>
+        <f>IF(B200="","",IFERROR(N200+VLOOKUP(E200,'Reference Data 기준데이터'!$A$8:$D$23,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="Q200" s="20" t="n"/>
@@ -18186,10 +16921,10 @@
       <formula1>'Reference Data 기준데이터'!$A$3:$A$5</formula1>
     </dataValidation>
     <dataValidation sqref="C5:C200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="Select part" type="list">
-      <formula1>'Reference Data 기준데이터'!$A$54:$A$59</formula1>
+      <formula1>'Reference Data 기준데이터'!$A$27:$A$32</formula1>
     </dataValidation>
     <dataValidation sqref="E5:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="Select test" type="list">
-      <formula1>'Reference Data 기준데이터'!$A$61:$A$75</formula1>
+      <formula1>'Reference Data 기준데이터'!$A$9:$A$23</formula1>
     </dataValidation>
     <dataValidation sqref="K5:K200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="Select review result" type="list">
       <formula1>"Under Review,Approved,Revision Needed"</formula1>
